--- a/research/traditional_assets/database/data/belgium/belgium_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_business_consumer_services.xlsx
@@ -1133,7 +1133,7 @@
         <v>26.9805447470817</v>
       </c>
       <c r="F2">
-        <v>4.57995375822485</v>
+        <v>4.57995375822484</v>
       </c>
       <c r="G2">
         <v>0.621981883142931</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09471852104142721</v>
+        <v>0.09451547473882364</v>
       </c>
       <c r="C2">
-        <v>93.42270101542969</v>
+        <v>92.65957673239534</v>
       </c>
       <c r="D2">
-        <v>83.02270101542969</v>
+        <v>83.20363677171255</v>
       </c>
       <c r="E2">
-        <v>-7.006003931721975</v>
+        <v>-6.061943892404755</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9440600393172198</v>
       </c>
       <c r="G2">
         <v>10.4</v>
@@ -1451,28 +1451,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04748621997765615</v>
       </c>
       <c r="N2">
-        <v>6.933999999999999</v>
+        <v>6.886513780022343</v>
       </c>
       <c r="O2">
-        <v>1.7335</v>
+        <v>1.721628445005586</v>
       </c>
       <c r="P2">
-        <v>5.2005</v>
+        <v>5.164885335016757</v>
       </c>
       <c r="Q2">
-        <v>9.5305</v>
+        <v>9.494885335016757</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09471852104142721</v>
+        <v>0.09508911589780167</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927492</v>
+        <v>0.9607366106313306</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.0213089873794</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09451547473882364</v>
+        <v>0.09431242843622009</v>
       </c>
       <c r="C3">
-        <v>92.65957673239534</v>
+        <v>91.89724281754781</v>
       </c>
       <c r="D3">
-        <v>83.20363677171255</v>
+        <v>83.38536289618224</v>
       </c>
       <c r="E3">
-        <v>-6.061943892404755</v>
+        <v>-5.117883853087536</v>
       </c>
       <c r="F3">
-        <v>0.9440600393172198</v>
+        <v>1.88812007863444</v>
       </c>
       <c r="G3">
         <v>10.4</v>
@@ -1533,28 +1533,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M3">
-        <v>0.04748621997765615</v>
+        <v>0.09497243995531231</v>
       </c>
       <c r="N3">
-        <v>6.886513780022343</v>
+        <v>6.839027560044687</v>
       </c>
       <c r="O3">
-        <v>1.721628445005586</v>
+        <v>1.709756890011172</v>
       </c>
       <c r="P3">
-        <v>5.164885335016757</v>
+        <v>5.129270670033515</v>
       </c>
       <c r="Q3">
-        <v>9.494885335016757</v>
+        <v>9.459270670033515</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09508911589780167</v>
+        <v>0.09546727391451029</v>
       </c>
       <c r="T3">
-        <v>0.9607366106313306</v>
+        <v>0.9681076142421281</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.0213089873794</v>
+        <v>73.01065449368971</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09431242843622009</v>
+        <v>0.09410938213361651</v>
       </c>
       <c r="C4">
-        <v>91.89724281754781</v>
+        <v>91.13570446098264</v>
       </c>
       <c r="D4">
-        <v>83.38536289618224</v>
+        <v>83.5678845789343</v>
       </c>
       <c r="E4">
-        <v>-5.117883853087536</v>
+        <v>-4.173823813770316</v>
       </c>
       <c r="F4">
-        <v>1.88812007863444</v>
+        <v>2.832180117951659</v>
       </c>
       <c r="G4">
         <v>10.4</v>
@@ -1615,28 +1615,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M4">
-        <v>0.09497243995531231</v>
+        <v>0.1424586599329684</v>
       </c>
       <c r="N4">
-        <v>6.839027560044687</v>
+        <v>6.791541340067031</v>
       </c>
       <c r="O4">
-        <v>1.709756890011172</v>
+        <v>1.697885335016758</v>
       </c>
       <c r="P4">
-        <v>5.129270670033515</v>
+        <v>5.093656005050273</v>
       </c>
       <c r="Q4">
-        <v>9.459270670033515</v>
+        <v>9.423656005050272</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09546727391451029</v>
+        <v>0.09585322900372836</v>
       </c>
       <c r="T4">
-        <v>0.9681076142421281</v>
+        <v>0.9756305973088181</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.01065449368971</v>
+        <v>48.67376966245982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09410938213361651</v>
+        <v>0.09390633583101293</v>
       </c>
       <c r="C5">
-        <v>91.13570446098264</v>
+        <v>90.37496689833722</v>
       </c>
       <c r="D5">
-        <v>83.5678845789343</v>
+        <v>83.75120705560609</v>
       </c>
       <c r="E5">
-        <v>-4.173823813770316</v>
+        <v>-3.229763774453096</v>
       </c>
       <c r="F5">
-        <v>2.832180117951659</v>
+        <v>3.776240157268879</v>
       </c>
       <c r="G5">
         <v>10.4</v>
@@ -1697,28 +1697,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1424586599329684</v>
+        <v>0.1899448799106246</v>
       </c>
       <c r="N5">
-        <v>6.791541340067031</v>
+        <v>6.744055120089374</v>
       </c>
       <c r="O5">
-        <v>1.697885335016758</v>
+        <v>1.686013780022344</v>
       </c>
       <c r="P5">
-        <v>5.093656005050273</v>
+        <v>5.058041340067031</v>
       </c>
       <c r="Q5">
-        <v>9.423656005050272</v>
+        <v>9.38804134006703</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09585322900372836</v>
+        <v>0.09624722482397181</v>
       </c>
       <c r="T5">
-        <v>0.9756305973088181</v>
+        <v>0.9833103091893977</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.67376966245982</v>
+        <v>36.50532724684486</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09390633583101293</v>
+        <v>0.09370328952840937</v>
       </c>
       <c r="C6">
-        <v>90.37496689833722</v>
+        <v>89.61503541129152</v>
       </c>
       <c r="D6">
-        <v>83.75120705560609</v>
+        <v>83.9353356078776</v>
       </c>
       <c r="E6">
-        <v>-3.229763774453096</v>
+        <v>-2.285703735135876</v>
       </c>
       <c r="F6">
-        <v>3.776240157268879</v>
+        <v>4.720300196586099</v>
       </c>
       <c r="G6">
         <v>10.4</v>
@@ -1779,28 +1779,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M6">
-        <v>0.1899448799106246</v>
+        <v>0.2374310998882808</v>
       </c>
       <c r="N6">
-        <v>6.744055120089374</v>
+        <v>6.696568900111719</v>
       </c>
       <c r="O6">
-        <v>1.686013780022344</v>
+        <v>1.67414222502793</v>
       </c>
       <c r="P6">
-        <v>5.058041340067031</v>
+        <v>5.022426675083789</v>
       </c>
       <c r="Q6">
-        <v>9.38804134006703</v>
+        <v>9.352426675083789</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09624722482397181</v>
+        <v>0.0966495152930625</v>
       </c>
       <c r="T6">
-        <v>0.9833103091893977</v>
+        <v>0.9911516992148314</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.50532724684486</v>
+        <v>29.20426179747588</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09370328952840937</v>
+        <v>0.09350024322580579</v>
       </c>
       <c r="C7">
-        <v>89.61503541129152</v>
+        <v>88.8559153280754</v>
       </c>
       <c r="D7">
-        <v>83.9353356078776</v>
+        <v>84.12027556397871</v>
       </c>
       <c r="E7">
-        <v>-2.285703735135876</v>
+        <v>-1.341643695818656</v>
       </c>
       <c r="F7">
-        <v>4.720300196586099</v>
+        <v>5.664360235903319</v>
       </c>
       <c r="G7">
         <v>10.4</v>
@@ -1861,28 +1861,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M7">
-        <v>0.2374310998882808</v>
+        <v>0.2849173198659369</v>
       </c>
       <c r="N7">
-        <v>6.696568900111719</v>
+        <v>6.649082680134063</v>
       </c>
       <c r="O7">
-        <v>1.67414222502793</v>
+        <v>1.662270670033516</v>
       </c>
       <c r="P7">
-        <v>5.022426675083789</v>
+        <v>4.986812010100547</v>
       </c>
       <c r="Q7">
-        <v>9.352426675083789</v>
+        <v>9.316812010100547</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0966495152930625</v>
+        <v>0.09706036513383595</v>
       </c>
       <c r="T7">
-        <v>0.9911516992148314</v>
+        <v>0.9991599273259127</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.20426179747588</v>
+        <v>24.33688483122991</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09350024322580579</v>
+        <v>0.09329719692320224</v>
       </c>
       <c r="C8">
-        <v>88.8559153280754</v>
+        <v>88.09761202398242</v>
       </c>
       <c r="D8">
-        <v>84.12027556397871</v>
+        <v>84.30603229920295</v>
       </c>
       <c r="E8">
-        <v>-1.341643695818656</v>
+        <v>-0.3975836565014363</v>
       </c>
       <c r="F8">
-        <v>5.664360235903318</v>
+        <v>6.608420275220539</v>
       </c>
       <c r="G8">
         <v>10.4</v>
@@ -1943,28 +1943,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M8">
-        <v>0.2849173198659369</v>
+        <v>0.3324035398435931</v>
       </c>
       <c r="N8">
-        <v>6.649082680134063</v>
+        <v>6.601596460156406</v>
       </c>
       <c r="O8">
-        <v>1.662270670033516</v>
+        <v>1.650399115039102</v>
       </c>
       <c r="P8">
-        <v>4.986812010100547</v>
+        <v>4.951197345117304</v>
       </c>
       <c r="Q8">
-        <v>9.316812010100547</v>
+        <v>9.281197345117304</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09706036513383595</v>
+        <v>0.09748005045505617</v>
       </c>
       <c r="T8">
-        <v>0.9991599273259127</v>
+        <v>1.007340375396372</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.33688483122991</v>
+        <v>20.86018699819706</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09329719692320224</v>
+        <v>0.09309415062059867</v>
       </c>
       <c r="C9">
-        <v>88.09761202398242</v>
+        <v>87.34013092189078</v>
       </c>
       <c r="D9">
-        <v>84.30603229920295</v>
+        <v>84.49261123642853</v>
       </c>
       <c r="E9">
-        <v>-0.3975836565014355</v>
+        <v>0.5464763828157837</v>
       </c>
       <c r="F9">
-        <v>6.608420275220539</v>
+        <v>7.552480314537759</v>
       </c>
       <c r="G9">
         <v>10.4</v>
@@ -2025,28 +2025,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M9">
-        <v>0.3324035398435931</v>
+        <v>0.3798897598212492</v>
       </c>
       <c r="N9">
-        <v>6.601596460156406</v>
+        <v>6.55411024017875</v>
       </c>
       <c r="O9">
-        <v>1.650399115039102</v>
+        <v>1.638527560044688</v>
       </c>
       <c r="P9">
-        <v>4.951197345117304</v>
+        <v>4.915582680134063</v>
       </c>
       <c r="Q9">
-        <v>9.281197345117304</v>
+        <v>9.245582680134063</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09748005045505617</v>
+        <v>0.09790885937021596</v>
       </c>
       <c r="T9">
-        <v>1.007340375396372</v>
+        <v>1.01569865929445</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.86018699819706</v>
+        <v>18.25266362342243</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09309415062059867</v>
+        <v>0.0928911043179951</v>
       </c>
       <c r="C10">
-        <v>87.34013092189078</v>
+        <v>86.58347749279096</v>
       </c>
       <c r="D10">
-        <v>84.49261123642853</v>
+        <v>84.68001784664594</v>
       </c>
       <c r="E10">
-        <v>0.5464763828157837</v>
+        <v>1.490536422133004</v>
       </c>
       <c r="F10">
-        <v>7.552480314537759</v>
+        <v>8.496540353854979</v>
       </c>
       <c r="G10">
         <v>10.4</v>
@@ -2107,28 +2107,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M10">
-        <v>0.3798897598212492</v>
+        <v>0.4273759797989054</v>
       </c>
       <c r="N10">
-        <v>6.55411024017875</v>
+        <v>6.506624020201094</v>
       </c>
       <c r="O10">
-        <v>1.638527560044688</v>
+        <v>1.626656005050273</v>
       </c>
       <c r="P10">
-        <v>4.915582680134063</v>
+        <v>4.87996801515082</v>
       </c>
       <c r="Q10">
-        <v>9.245582680134063</v>
+        <v>9.209968015150821</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09790885937021596</v>
+        <v>0.09834709265713747</v>
       </c>
       <c r="T10">
-        <v>1.01569865929445</v>
+        <v>1.024240641739739</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.25266362342243</v>
+        <v>16.2245898874866</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0928911043179951</v>
+        <v>0.09268805801539154</v>
       </c>
       <c r="C11">
-        <v>86.58347749279096</v>
+        <v>85.82765725632044</v>
       </c>
       <c r="D11">
-        <v>84.68001784664594</v>
+        <v>84.86825764949262</v>
       </c>
       <c r="E11">
-        <v>1.490536422133004</v>
+        <v>2.434596461450222</v>
       </c>
       <c r="F11">
-        <v>8.496540353854979</v>
+        <v>9.440600393172197</v>
       </c>
       <c r="G11">
         <v>10.4</v>
@@ -2189,28 +2189,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M11">
-        <v>0.4273759797989054</v>
+        <v>0.4748621997765615</v>
       </c>
       <c r="N11">
-        <v>6.506624020201094</v>
+        <v>6.459137800223438</v>
       </c>
       <c r="O11">
-        <v>1.626656005050273</v>
+        <v>1.614784450055859</v>
       </c>
       <c r="P11">
-        <v>4.87996801515082</v>
+        <v>4.844353350167578</v>
       </c>
       <c r="Q11">
-        <v>9.209968015150821</v>
+        <v>9.174353350167578</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09834709265713747</v>
+        <v>0.09879506446154615</v>
       </c>
       <c r="T11">
-        <v>1.024240641739739</v>
+        <v>1.032972446017145</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.2245898874866</v>
+        <v>14.60213089873795</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09268805801539154</v>
+        <v>0.09248501171278796</v>
       </c>
       <c r="C12">
-        <v>85.82765725632042</v>
+        <v>85.07267578130566</v>
       </c>
       <c r="D12">
-        <v>84.86825764949262</v>
+        <v>85.05733621379508</v>
       </c>
       <c r="E12">
-        <v>2.434596461450224</v>
+        <v>3.378656500767444</v>
       </c>
       <c r="F12">
-        <v>9.440600393172199</v>
+        <v>10.38466043248942</v>
       </c>
       <c r="G12">
         <v>10.4</v>
@@ -2271,28 +2271,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M12">
-        <v>0.4748621997765616</v>
+        <v>0.5223484197542178</v>
       </c>
       <c r="N12">
-        <v>6.459137800223438</v>
+        <v>6.411651580245781</v>
       </c>
       <c r="O12">
-        <v>1.614784450055859</v>
+        <v>1.602912895061445</v>
       </c>
       <c r="P12">
-        <v>4.844353350167578</v>
+        <v>4.808738685184336</v>
       </c>
       <c r="Q12">
-        <v>9.174353350167578</v>
+        <v>9.138738685184336</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09879506446154615</v>
+        <v>0.09925310304807637</v>
       </c>
       <c r="T12">
-        <v>1.032972446017145</v>
+        <v>1.041900470615392</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.60213089873794</v>
+        <v>13.27466445339813</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09248501171278796</v>
+        <v>0.09241696541018439</v>
       </c>
       <c r="C13">
-        <v>85.07267578130566</v>
+        <v>84.19216970152348</v>
       </c>
       <c r="D13">
-        <v>85.05733621379508</v>
+        <v>85.12089017333011</v>
       </c>
       <c r="E13">
-        <v>3.378656500767444</v>
+        <v>4.322716540084662</v>
       </c>
       <c r="F13">
-        <v>10.38466043248942</v>
+        <v>11.32872047180664</v>
       </c>
       <c r="G13">
         <v>10.4</v>
@@ -2353,45 +2353,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M13">
-        <v>0.5223484197542178</v>
+        <v>0.5868277204395838</v>
       </c>
       <c r="N13">
-        <v>6.411651580245781</v>
+        <v>6.347172279560415</v>
       </c>
       <c r="O13">
-        <v>1.602912895061445</v>
+        <v>1.586793069890104</v>
       </c>
       <c r="P13">
-        <v>4.808738685184336</v>
+        <v>4.760379209670312</v>
       </c>
       <c r="Q13">
-        <v>9.138738685184336</v>
+        <v>9.090379209670312</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09925310304807637</v>
+        <v>0.09972155160248226</v>
       </c>
       <c r="T13">
-        <v>1.041900470615392</v>
+        <v>1.051031404863598</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.27466445339813</v>
+        <v>11.81607439199676</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09241696541018439</v>
+        <v>0.09222516910758081</v>
       </c>
       <c r="C14">
-        <v>84.19216970152348</v>
+        <v>83.42775597040433</v>
       </c>
       <c r="D14">
-        <v>85.12089017333011</v>
+        <v>85.30053648152818</v>
       </c>
       <c r="E14">
-        <v>4.322716540084662</v>
+        <v>5.266776579401884</v>
       </c>
       <c r="F14">
-        <v>11.32872047180664</v>
+        <v>12.27278051112386</v>
       </c>
       <c r="G14">
         <v>10.4</v>
@@ -2435,28 +2435,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M14">
-        <v>0.5868277204395838</v>
+        <v>0.6357300304762159</v>
       </c>
       <c r="N14">
-        <v>6.347172279560415</v>
+        <v>6.298269969523783</v>
       </c>
       <c r="O14">
-        <v>1.586793069890104</v>
+        <v>1.574567492380946</v>
       </c>
       <c r="P14">
-        <v>4.760379209670312</v>
+        <v>4.723702477142838</v>
       </c>
       <c r="Q14">
-        <v>9.090379209670312</v>
+        <v>9.053702477142838</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09972155160248226</v>
+        <v>0.1002007690891734</v>
       </c>
       <c r="T14">
-        <v>1.051031404863598</v>
+        <v>1.060372245646247</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.81607439199676</v>
+        <v>10.90714559261239</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09222516910758081</v>
+        <v>0.09203337280497725</v>
       </c>
       <c r="C15">
-        <v>83.42775597040433</v>
+        <v>82.66410212446179</v>
       </c>
       <c r="D15">
-        <v>85.30053648152818</v>
+        <v>85.48094267490286</v>
       </c>
       <c r="E15">
-        <v>5.266776579401884</v>
+        <v>6.210836618719104</v>
       </c>
       <c r="F15">
-        <v>12.27278051112386</v>
+        <v>13.21684055044108</v>
       </c>
       <c r="G15">
         <v>10.4</v>
@@ -2517,28 +2517,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M15">
-        <v>0.6357300304762159</v>
+        <v>0.6846323405128478</v>
       </c>
       <c r="N15">
-        <v>6.298269969523783</v>
+        <v>6.249367659487151</v>
       </c>
       <c r="O15">
-        <v>1.574567492380946</v>
+        <v>1.562341914871788</v>
       </c>
       <c r="P15">
-        <v>4.723702477142838</v>
+        <v>4.687025744615363</v>
       </c>
       <c r="Q15">
-        <v>9.053702477142838</v>
+        <v>9.017025744615363</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1002007690891734</v>
+        <v>0.1006911311685782</v>
       </c>
       <c r="T15">
-        <v>1.060372245646247</v>
+        <v>1.069930315284306</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.90714559261239</v>
+        <v>10.12806376456865</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09203337280497725</v>
+        <v>0.0920328265023737</v>
       </c>
       <c r="C16">
-        <v>82.66410212446179</v>
+        <v>81.7205570346424</v>
       </c>
       <c r="D16">
-        <v>85.48094267490286</v>
+        <v>85.48145762440069</v>
       </c>
       <c r="E16">
-        <v>6.210836618719104</v>
+        <v>7.154896658036324</v>
       </c>
       <c r="F16">
-        <v>13.21684055044108</v>
+        <v>14.1609005897583</v>
       </c>
       <c r="G16">
         <v>10.4</v>
@@ -2599,45 +2599,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M16">
-        <v>0.6846323405128478</v>
+        <v>0.757608181552069</v>
       </c>
       <c r="N16">
-        <v>6.249367659487151</v>
+        <v>6.176391818447931</v>
       </c>
       <c r="O16">
-        <v>1.562341914871788</v>
+        <v>1.544097954611983</v>
       </c>
       <c r="P16">
-        <v>4.687025744615363</v>
+        <v>4.632293863835947</v>
       </c>
       <c r="Q16">
-        <v>9.017025744615363</v>
+        <v>8.962293863835948</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1006911311685782</v>
+        <v>0.1011930311792632</v>
       </c>
       <c r="T16">
-        <v>1.069930315284306</v>
+        <v>1.079713280678554</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.12806376456865</v>
+        <v>9.15248827671674</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0920328265023737</v>
+        <v>0.09185378019977011</v>
       </c>
       <c r="C17">
-        <v>81.7205570346424</v>
+        <v>80.94560246124772</v>
       </c>
       <c r="D17">
-        <v>85.48145762440069</v>
+        <v>85.65056309032323</v>
       </c>
       <c r="E17">
-        <v>7.154896658036322</v>
+        <v>8.098956697353543</v>
       </c>
       <c r="F17">
-        <v>14.1609005897583</v>
+        <v>15.10496062907552</v>
       </c>
       <c r="G17">
         <v>10.4</v>
@@ -2681,28 +2681,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M17">
-        <v>0.7576081815520689</v>
+        <v>0.8081153936555402</v>
       </c>
       <c r="N17">
-        <v>6.176391818447931</v>
+        <v>6.125884606344459</v>
       </c>
       <c r="O17">
-        <v>1.544097954611983</v>
+        <v>1.531471151586115</v>
       </c>
       <c r="P17">
-        <v>4.632293863835947</v>
+        <v>4.594413454758344</v>
       </c>
       <c r="Q17">
-        <v>8.962293863835948</v>
+        <v>8.924413454758344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1011930311792632</v>
+        <v>0.1017068811902025</v>
       </c>
       <c r="T17">
-        <v>1.079713280678554</v>
+        <v>1.089729173820285</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.152488276716742</v>
+        <v>8.580457759421945</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09185378019977011</v>
+        <v>0.09167473389716656</v>
       </c>
       <c r="C18">
-        <v>80.94560246124772</v>
+        <v>80.17131828687218</v>
       </c>
       <c r="D18">
-        <v>85.65056309032323</v>
+        <v>85.82033895526492</v>
       </c>
       <c r="E18">
-        <v>8.098956697353543</v>
+        <v>9.043016736670765</v>
       </c>
       <c r="F18">
-        <v>15.10496062907552</v>
+        <v>16.04902066839274</v>
       </c>
       <c r="G18">
         <v>10.4</v>
@@ -2763,28 +2763,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M18">
-        <v>0.8081153936555402</v>
+        <v>0.8586226057590115</v>
       </c>
       <c r="N18">
-        <v>6.125884606344459</v>
+        <v>6.075377394240988</v>
       </c>
       <c r="O18">
-        <v>1.531471151586115</v>
+        <v>1.518844348560247</v>
       </c>
       <c r="P18">
-        <v>4.594413454758344</v>
+        <v>4.556533045680741</v>
       </c>
       <c r="Q18">
-        <v>8.924413454758344</v>
+        <v>8.886533045680741</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1017068811902025</v>
+        <v>0.1022331131291163</v>
       </c>
       <c r="T18">
-        <v>1.089729173820285</v>
+        <v>1.099986413784708</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.580457759421945</v>
+        <v>8.075724950044183</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09167473389716656</v>
+        <v>0.09149568759456299</v>
       </c>
       <c r="C19">
-        <v>80.17131828687218</v>
+        <v>79.39770850601249</v>
       </c>
       <c r="D19">
-        <v>85.82033895526492</v>
+        <v>85.99078921372245</v>
       </c>
       <c r="E19">
-        <v>9.043016736670765</v>
+        <v>9.987076775987983</v>
       </c>
       <c r="F19">
-        <v>16.04902066839274</v>
+        <v>16.99308070770996</v>
       </c>
       <c r="G19">
         <v>10.4</v>
@@ -2845,28 +2845,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M19">
-        <v>0.8586226057590115</v>
+        <v>0.9091298178624827</v>
       </c>
       <c r="N19">
-        <v>6.075377394240988</v>
+        <v>6.024870182137517</v>
       </c>
       <c r="O19">
-        <v>1.518844348560247</v>
+        <v>1.506217545534379</v>
       </c>
       <c r="P19">
-        <v>4.556533045680741</v>
+        <v>4.518652636603138</v>
       </c>
       <c r="Q19">
-        <v>8.886533045680741</v>
+        <v>8.848652636603138</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1022331131291163</v>
+        <v>0.1027721799933695</v>
       </c>
       <c r="T19">
-        <v>1.099986413784708</v>
+        <v>1.110493830333628</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.075724950044183</v>
+        <v>7.627073563930618</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09149568759456297</v>
+        <v>0.09143064129195944</v>
       </c>
       <c r="C20">
-        <v>79.39770850601249</v>
+        <v>78.51573967461637</v>
       </c>
       <c r="D20">
-        <v>85.99078921372245</v>
+        <v>86.05288042164354</v>
       </c>
       <c r="E20">
-        <v>9.987076775987983</v>
+        <v>10.9311368153052</v>
       </c>
       <c r="F20">
-        <v>16.99308070770996</v>
+        <v>17.93714074702718</v>
       </c>
       <c r="G20">
         <v>10.4</v>
@@ -2927,45 +2927,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M20">
-        <v>0.9091298178624827</v>
+        <v>0.9739867425635756</v>
       </c>
       <c r="N20">
-        <v>6.024870182137517</v>
+        <v>5.960013257436423</v>
       </c>
       <c r="O20">
-        <v>1.506217545534379</v>
+        <v>1.490003314359106</v>
       </c>
       <c r="P20">
-        <v>4.518652636603138</v>
+        <v>4.470009943077318</v>
       </c>
       <c r="Q20">
-        <v>8.848652636603138</v>
+        <v>8.800009943077317</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1027721799933695</v>
+        <v>0.1033245571505672</v>
       </c>
       <c r="T20">
-        <v>1.110493830333628</v>
+        <v>1.121260689266474</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.627073563930618</v>
+        <v>7.119193410938436</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09143064129195944</v>
+        <v>0.09125759498935586</v>
       </c>
       <c r="C21">
-        <v>78.51573967461637</v>
+        <v>77.7373017626547</v>
       </c>
       <c r="D21">
-        <v>86.05288042164354</v>
+        <v>86.21850254899908</v>
       </c>
       <c r="E21">
-        <v>10.9311368153052</v>
+        <v>11.87519685462242</v>
       </c>
       <c r="F21">
-        <v>17.93714074702718</v>
+        <v>18.8812007863444</v>
       </c>
       <c r="G21">
         <v>10.4</v>
@@ -3009,28 +3009,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M21">
-        <v>0.9739867425635756</v>
+        <v>1.025249202698501</v>
       </c>
       <c r="N21">
-        <v>5.960013257436423</v>
+        <v>5.908750797301499</v>
       </c>
       <c r="O21">
-        <v>1.490003314359106</v>
+        <v>1.477187699325375</v>
       </c>
       <c r="P21">
-        <v>4.470009943077318</v>
+        <v>4.431563097976124</v>
       </c>
       <c r="Q21">
-        <v>8.800009943077317</v>
+        <v>8.761563097976124</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1033245571505672</v>
+        <v>0.1038907437366948</v>
       </c>
       <c r="T21">
-        <v>1.121260689266474</v>
+        <v>1.13229671967264</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.119193410938436</v>
+        <v>6.763233740391515</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09125759498935586</v>
+        <v>0.09108454868675228</v>
       </c>
       <c r="C22">
-        <v>77.7373017626547</v>
+        <v>76.9595026110776</v>
       </c>
       <c r="D22">
-        <v>86.21850254899908</v>
+        <v>86.38476343673921</v>
       </c>
       <c r="E22">
-        <v>11.87519685462242</v>
+        <v>12.81925689393965</v>
       </c>
       <c r="F22">
-        <v>18.8812007863444</v>
+        <v>19.82526082566162</v>
       </c>
       <c r="G22">
         <v>10.4</v>
@@ -3091,28 +3091,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M22">
-        <v>1.025249202698501</v>
+        <v>1.076511662833426</v>
       </c>
       <c r="N22">
-        <v>5.908750797301499</v>
+        <v>5.857488337166574</v>
       </c>
       <c r="O22">
-        <v>1.477187699325375</v>
+        <v>1.464372084291643</v>
       </c>
       <c r="P22">
-        <v>4.431563097976124</v>
+        <v>4.393116252874931</v>
       </c>
       <c r="Q22">
-        <v>8.761563097976124</v>
+        <v>8.723116252874931</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1038907437366948</v>
+        <v>0.1044712641604459</v>
       </c>
       <c r="T22">
-        <v>1.13229671967264</v>
+        <v>1.143612143253645</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.763233740391515</v>
+        <v>6.441174990849061</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09108454868675228</v>
+        <v>0.0909115023841487</v>
       </c>
       <c r="C23">
-        <v>76.9595026110776</v>
+        <v>76.18234592231748</v>
       </c>
       <c r="D23">
-        <v>86.38476343673921</v>
+        <v>86.55166678729631</v>
       </c>
       <c r="E23">
-        <v>12.81925689393964</v>
+        <v>13.76331693325686</v>
       </c>
       <c r="F23">
-        <v>19.82526082566162</v>
+        <v>20.76932086497884</v>
       </c>
       <c r="G23">
         <v>10.4</v>
@@ -3173,28 +3173,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M23">
-        <v>1.076511662833426</v>
+        <v>1.127774122968351</v>
       </c>
       <c r="N23">
-        <v>5.857488337166574</v>
+        <v>5.806225877031649</v>
       </c>
       <c r="O23">
-        <v>1.464372084291643</v>
+        <v>1.451556469257912</v>
       </c>
       <c r="P23">
-        <v>4.393116252874931</v>
+        <v>4.354669407773736</v>
       </c>
       <c r="Q23">
-        <v>8.723116252874931</v>
+        <v>8.684669407773736</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1044712641604459</v>
+        <v>0.1050666697232676</v>
       </c>
       <c r="T23">
-        <v>1.143612143253645</v>
+        <v>1.155217705900831</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.441174990849063</v>
+        <v>6.148394309446831</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0909115023841487</v>
+        <v>0.09091095608154516</v>
       </c>
       <c r="C24">
-        <v>76.18234592231748</v>
+        <v>75.23881381372451</v>
       </c>
       <c r="D24">
-        <v>86.55166678729631</v>
+        <v>86.55219471802056</v>
       </c>
       <c r="E24">
-        <v>13.76331693325686</v>
+        <v>14.70737697257408</v>
       </c>
       <c r="F24">
-        <v>20.76932086497884</v>
+        <v>21.71338090429606</v>
       </c>
       <c r="G24">
         <v>10.4</v>
@@ -3255,45 +3255,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M24">
-        <v>1.127774122968351</v>
+        <v>1.200749964007572</v>
       </c>
       <c r="N24">
-        <v>5.806225877031649</v>
+        <v>5.733250035992428</v>
       </c>
       <c r="O24">
-        <v>1.451556469257912</v>
+        <v>1.433312508998107</v>
       </c>
       <c r="P24">
-        <v>4.354669407773736</v>
+        <v>4.299937526994321</v>
       </c>
       <c r="Q24">
-        <v>8.684669407773736</v>
+        <v>8.629937526994322</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1050666697232676</v>
+        <v>0.1056775403656431</v>
       </c>
       <c r="T24">
-        <v>1.155217705900831</v>
+        <v>1.167124711733657</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.148394309446831</v>
+        <v>5.774724303848719</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09091095608154516</v>
+        <v>0.09074540977894159</v>
       </c>
       <c r="C25">
-        <v>75.23881381372451</v>
+        <v>74.45503006375391</v>
       </c>
       <c r="D25">
-        <v>86.55219471802056</v>
+        <v>86.71247100736718</v>
       </c>
       <c r="E25">
-        <v>14.70737697257408</v>
+        <v>15.6514370118913</v>
       </c>
       <c r="F25">
-        <v>21.71338090429606</v>
+        <v>22.65744094361328</v>
       </c>
       <c r="G25">
         <v>10.4</v>
@@ -3337,28 +3337,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M25">
-        <v>1.200749964007572</v>
+        <v>1.252956484181814</v>
       </c>
       <c r="N25">
-        <v>5.733250035992428</v>
+        <v>5.681043515818185</v>
       </c>
       <c r="O25">
-        <v>1.433312508998107</v>
+        <v>1.420260878954546</v>
       </c>
       <c r="P25">
-        <v>4.299937526994321</v>
+        <v>4.260782636863639</v>
       </c>
       <c r="Q25">
-        <v>8.629937526994322</v>
+        <v>8.59078263686364</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1056775403656431</v>
+        <v>0.1063044865512389</v>
       </c>
       <c r="T25">
-        <v>1.167124711733657</v>
+        <v>1.179345059825242</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.774724303848719</v>
+        <v>5.534110791188355</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09074540977894159</v>
+        <v>0.09057986347633801</v>
       </c>
       <c r="C26">
-        <v>74.45503006375392</v>
+        <v>73.67184101035667</v>
       </c>
       <c r="D26">
-        <v>86.71247100736718</v>
+        <v>86.87334199328716</v>
       </c>
       <c r="E26">
-        <v>15.6514370118913</v>
+        <v>16.59549705120852</v>
       </c>
       <c r="F26">
-        <v>22.65744094361327</v>
+        <v>23.6015009829305</v>
       </c>
       <c r="G26">
         <v>10.4</v>
@@ -3419,28 +3419,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M26">
-        <v>1.252956484181814</v>
+        <v>1.305163004356056</v>
       </c>
       <c r="N26">
-        <v>5.681043515818185</v>
+        <v>5.628836995643943</v>
       </c>
       <c r="O26">
-        <v>1.420260878954546</v>
+        <v>1.407209248910986</v>
       </c>
       <c r="P26">
-        <v>4.260782636863639</v>
+        <v>4.221627746732957</v>
       </c>
       <c r="Q26">
-        <v>8.59078263686364</v>
+        <v>8.551627746732958</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1063044865512389</v>
+        <v>0.106948151301784</v>
       </c>
       <c r="T26">
-        <v>1.179345059825242</v>
+        <v>1.191891283865937</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.534110791188355</v>
+        <v>5.312746359540821</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09057986347633801</v>
+        <v>0.09041431717373444</v>
       </c>
       <c r="C27">
-        <v>73.67184101035667</v>
+        <v>72.88924996956933</v>
       </c>
       <c r="D27">
-        <v>86.87334199328716</v>
+        <v>87.03481099181704</v>
       </c>
       <c r="E27">
-        <v>16.59549705120852</v>
+        <v>17.53955709052574</v>
       </c>
       <c r="F27">
-        <v>23.6015009829305</v>
+        <v>24.54556102224772</v>
       </c>
       <c r="G27">
         <v>10.4</v>
@@ -3501,28 +3501,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M27">
-        <v>1.305163004356056</v>
+        <v>1.357369524530299</v>
       </c>
       <c r="N27">
-        <v>5.628836995643943</v>
+        <v>5.576630475469701</v>
       </c>
       <c r="O27">
-        <v>1.407209248910986</v>
+        <v>1.394157618867425</v>
       </c>
       <c r="P27">
-        <v>4.221627746732957</v>
+        <v>4.182472856602276</v>
       </c>
       <c r="Q27">
-        <v>8.551627746732958</v>
+        <v>8.512472856602276</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.106948151301784</v>
+        <v>0.1076092123969384</v>
       </c>
       <c r="T27">
-        <v>1.191891283865937</v>
+        <v>1.204776595042866</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.312746359540821</v>
+        <v>5.108409961096942</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09041431717373444</v>
+        <v>0.09024877087113087</v>
       </c>
       <c r="C28">
-        <v>72.88924996956933</v>
+        <v>72.10726028212808</v>
       </c>
       <c r="D28">
-        <v>87.03481099181704</v>
+        <v>87.19688134369301</v>
       </c>
       <c r="E28">
-        <v>17.53955709052574</v>
+        <v>18.48361712984296</v>
       </c>
       <c r="F28">
-        <v>24.54556102224772</v>
+        <v>25.48962106156494</v>
       </c>
       <c r="G28">
         <v>10.4</v>
@@ -3583,28 +3583,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M28">
-        <v>1.357369524530299</v>
+        <v>1.409576044704541</v>
       </c>
       <c r="N28">
-        <v>5.576630475469701</v>
+        <v>5.524423955295458</v>
       </c>
       <c r="O28">
-        <v>1.394157618867425</v>
+        <v>1.381105988823865</v>
       </c>
       <c r="P28">
-        <v>4.182472856602276</v>
+        <v>4.143317966471594</v>
       </c>
       <c r="Q28">
-        <v>8.512472856602276</v>
+        <v>8.473317966471594</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1076092123969384</v>
+        <v>0.1082883847549738</v>
       </c>
       <c r="T28">
-        <v>1.204776595042866</v>
+        <v>1.21801492844382</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.108409961096942</v>
+        <v>4.919209592167427</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09024877087113087</v>
+        <v>0.09008322456852731</v>
       </c>
       <c r="C29">
-        <v>72.10726028212808</v>
+        <v>71.32587531369911</v>
       </c>
       <c r="D29">
-        <v>87.19688134369301</v>
+        <v>87.35955641458126</v>
       </c>
       <c r="E29">
-        <v>18.48361712984296</v>
+        <v>19.42767716916018</v>
       </c>
       <c r="F29">
-        <v>25.48962106156494</v>
+        <v>26.43368110088216</v>
       </c>
       <c r="G29">
         <v>10.4</v>
@@ -3665,28 +3665,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M29">
-        <v>1.409576044704541</v>
+        <v>1.461782564878783</v>
       </c>
       <c r="N29">
-        <v>5.524423955295458</v>
+        <v>5.472217435121216</v>
       </c>
       <c r="O29">
-        <v>1.381105988823865</v>
+        <v>1.368054358780304</v>
       </c>
       <c r="P29">
-        <v>4.143317966471594</v>
+        <v>4.104163076340912</v>
       </c>
       <c r="Q29">
-        <v>8.473317966471594</v>
+        <v>8.434163076340912</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1082883847549738</v>
+        <v>0.1089864230118435</v>
       </c>
       <c r="T29">
-        <v>1.21801492844382</v>
+        <v>1.231620993328135</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.919209592167427</v>
+        <v>4.743523535304304</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09008322456852731</v>
+        <v>0.08991767826592374</v>
       </c>
       <c r="C30">
-        <v>71.32587531369911</v>
+        <v>70.54509845511163</v>
       </c>
       <c r="D30">
-        <v>87.35955641458126</v>
+        <v>87.522839595311</v>
       </c>
       <c r="E30">
-        <v>19.42767716916018</v>
+        <v>20.37173720847741</v>
       </c>
       <c r="F30">
-        <v>26.43368110088216</v>
+        <v>27.37774114019938</v>
       </c>
       <c r="G30">
         <v>10.4</v>
@@ -3747,28 +3747,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M30">
-        <v>1.461782564878783</v>
+        <v>1.513989085053026</v>
       </c>
       <c r="N30">
-        <v>5.472217435121216</v>
+        <v>5.420010914946974</v>
       </c>
       <c r="O30">
-        <v>1.368054358780304</v>
+        <v>1.355002728736743</v>
       </c>
       <c r="P30">
-        <v>4.104163076340912</v>
+        <v>4.06500818621023</v>
       </c>
       <c r="Q30">
-        <v>8.434163076340912</v>
+        <v>8.39500818621023</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1089864230118435</v>
+        <v>0.1097041243182025</v>
       </c>
       <c r="T30">
-        <v>1.231620993328135</v>
+        <v>1.24561032764581</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.743523535304304</v>
+        <v>4.579953758224844</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08991767826592374</v>
+        <v>0.09031463196332018</v>
       </c>
       <c r="C31">
-        <v>70.54509845511163</v>
+        <v>69.21052970149499</v>
       </c>
       <c r="D31">
-        <v>87.522839595311</v>
+        <v>87.13233088101158</v>
       </c>
       <c r="E31">
-        <v>20.3717372084774</v>
+        <v>21.31579724779462</v>
       </c>
       <c r="F31">
-        <v>27.37774114019937</v>
+        <v>28.32180117951659</v>
       </c>
       <c r="G31">
         <v>10.4</v>
@@ -3829,45 +3829,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M31">
-        <v>1.513989085053025</v>
+        <v>1.637000108176059</v>
       </c>
       <c r="N31">
-        <v>5.420010914946974</v>
+        <v>5.29699989182394</v>
       </c>
       <c r="O31">
-        <v>1.355002728736743</v>
+        <v>1.324249972955985</v>
       </c>
       <c r="P31">
-        <v>4.06500818621023</v>
+        <v>3.972749918867955</v>
       </c>
       <c r="Q31">
-        <v>8.39500818621023</v>
+        <v>8.302749918867956</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1097041243182025</v>
+        <v>0.1104423313761717</v>
       </c>
       <c r="T31">
-        <v>1.24561032764581</v>
+        <v>1.259999357229704</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.579953758224846</v>
+        <v>4.235796910072194</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09031463196332018</v>
+        <v>0.09016783566071659</v>
       </c>
       <c r="C32">
-        <v>69.21052970149499</v>
+        <v>68.41047583435541</v>
       </c>
       <c r="D32">
-        <v>87.13233088101158</v>
+        <v>87.27633705318922</v>
       </c>
       <c r="E32">
-        <v>21.31579724779462</v>
+        <v>22.25985728711184</v>
       </c>
       <c r="F32">
-        <v>28.32180117951659</v>
+        <v>29.26586121883382</v>
       </c>
       <c r="G32">
         <v>10.4</v>
@@ -3911,28 +3911,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M32">
-        <v>1.637000108176059</v>
+        <v>1.691566778448595</v>
       </c>
       <c r="N32">
-        <v>5.29699989182394</v>
+        <v>5.242433221551405</v>
       </c>
       <c r="O32">
-        <v>1.324249972955985</v>
+        <v>1.310608305387851</v>
       </c>
       <c r="P32">
-        <v>3.972749918867955</v>
+        <v>3.931824916163554</v>
       </c>
       <c r="Q32">
-        <v>8.302749918867956</v>
+        <v>8.261824916163555</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1104423313761717</v>
+        <v>0.111201935740169</v>
       </c>
       <c r="T32">
-        <v>1.259999357229704</v>
+        <v>1.274805460134871</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.235796910072194</v>
+        <v>4.099158300069865</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09016783566071659</v>
+        <v>0.09086103935811303</v>
       </c>
       <c r="C33">
-        <v>68.41047583435541</v>
+        <v>66.79053870324464</v>
       </c>
       <c r="D33">
-        <v>87.27633705318922</v>
+        <v>86.60045996139566</v>
       </c>
       <c r="E33">
-        <v>22.25985728711184</v>
+        <v>23.20391732642906</v>
       </c>
       <c r="F33">
-        <v>29.26586121883382</v>
+        <v>30.20992125815103</v>
       </c>
       <c r="G33">
         <v>10.4</v>
@@ -3993,45 +3993,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M33">
-        <v>1.691566778448595</v>
+        <v>1.851868173124658</v>
       </c>
       <c r="N33">
-        <v>5.242433221551405</v>
+        <v>5.082131826875341</v>
       </c>
       <c r="O33">
-        <v>1.310608305387851</v>
+        <v>1.270532956718835</v>
       </c>
       <c r="P33">
-        <v>3.931824916163554</v>
+        <v>3.811598870156506</v>
       </c>
       <c r="Q33">
-        <v>8.261824916163555</v>
+        <v>8.141598870156507</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.111201935740169</v>
+        <v>0.1119838814089898</v>
       </c>
       <c r="T33">
-        <v>1.274805460134871</v>
+        <v>1.290047036654896</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.099158300069865</v>
+        <v>3.744326999421485</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09086103935811303</v>
+        <v>0.09074049305550946</v>
       </c>
       <c r="C34">
-        <v>66.79053870324464</v>
+        <v>65.96325899118187</v>
       </c>
       <c r="D34">
-        <v>86.60045996139566</v>
+        <v>86.71724028865012</v>
       </c>
       <c r="E34">
-        <v>23.20391732642906</v>
+        <v>24.14797736574628</v>
       </c>
       <c r="F34">
-        <v>30.20992125815103</v>
+        <v>31.15398129746826</v>
       </c>
       <c r="G34">
         <v>10.4</v>
@@ -4075,28 +4075,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M34">
-        <v>1.851868173124658</v>
+        <v>1.909739053534804</v>
       </c>
       <c r="N34">
-        <v>5.082131826875341</v>
+        <v>5.024260946465195</v>
       </c>
       <c r="O34">
-        <v>1.270532956718835</v>
+        <v>1.256065236616299</v>
       </c>
       <c r="P34">
-        <v>3.811598870156506</v>
+        <v>3.768195709848897</v>
       </c>
       <c r="Q34">
-        <v>8.141598870156507</v>
+        <v>8.098195709848897</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1119838814089898</v>
+        <v>0.1127891687395664</v>
       </c>
       <c r="T34">
-        <v>1.290047036654896</v>
+        <v>1.305743585608354</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.744326999421485</v>
+        <v>3.630862544893561</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09074049305550946</v>
+        <v>0.09061994675290588</v>
       </c>
       <c r="C35">
-        <v>65.96325899118187</v>
+        <v>65.13629465989135</v>
       </c>
       <c r="D35">
-        <v>86.71724028865012</v>
+        <v>86.83433599667681</v>
       </c>
       <c r="E35">
-        <v>24.14797736574628</v>
+        <v>25.0920374050635</v>
       </c>
       <c r="F35">
-        <v>31.15398129746826</v>
+        <v>32.09804133678548</v>
       </c>
       <c r="G35">
         <v>10.4</v>
@@ -4157,28 +4157,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M35">
-        <v>1.909739053534804</v>
+        <v>1.96760993394495</v>
       </c>
       <c r="N35">
-        <v>5.024260946465195</v>
+        <v>4.96639006605505</v>
       </c>
       <c r="O35">
-        <v>1.256065236616299</v>
+        <v>1.241597516513762</v>
       </c>
       <c r="P35">
-        <v>3.768195709848897</v>
+        <v>3.724792549541287</v>
       </c>
       <c r="Q35">
-        <v>8.098195709848897</v>
+        <v>8.054792549541288</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1127891687395664</v>
+        <v>0.1136188587165241</v>
       </c>
       <c r="T35">
-        <v>1.305743585608354</v>
+        <v>1.321915787560402</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.630862544893561</v>
+        <v>3.52407247004375</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09061994675290588</v>
+        <v>0.09123440045030232</v>
       </c>
       <c r="C36">
-        <v>65.13629465989135</v>
+        <v>63.59864906632736</v>
       </c>
       <c r="D36">
-        <v>86.83433599667681</v>
+        <v>86.24075044243006</v>
       </c>
       <c r="E36">
-        <v>25.0920374050635</v>
+        <v>26.03609744438073</v>
       </c>
       <c r="F36">
-        <v>32.09804133678548</v>
+        <v>33.0421013761027</v>
       </c>
       <c r="G36">
         <v>10.4</v>
@@ -4239,45 +4239,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M36">
-        <v>1.96760993394495</v>
+        <v>2.117998698208183</v>
       </c>
       <c r="N36">
-        <v>4.96639006605505</v>
+        <v>4.816001301791816</v>
       </c>
       <c r="O36">
-        <v>1.241597516513762</v>
+        <v>1.204000325447954</v>
       </c>
       <c r="P36">
-        <v>3.724792549541287</v>
+        <v>3.612000976343862</v>
       </c>
       <c r="Q36">
-        <v>8.054792549541288</v>
+        <v>7.942000976343863</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1136188587165241</v>
+        <v>0.1144740776158497</v>
       </c>
       <c r="T36">
-        <v>1.321915787560402</v>
+        <v>1.338585595726359</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.52407247004375</v>
+        <v>3.273845260559475</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09123440045030232</v>
+        <v>0.09113485414769874</v>
       </c>
       <c r="C37">
-        <v>63.59864906632736</v>
+        <v>62.75020304403026</v>
       </c>
       <c r="D37">
-        <v>86.24075044243006</v>
+        <v>86.33636445945017</v>
       </c>
       <c r="E37">
-        <v>26.03609744438073</v>
+        <v>26.98015748369794</v>
       </c>
       <c r="F37">
-        <v>33.0421013761027</v>
+        <v>33.98616141541991</v>
       </c>
       <c r="G37">
         <v>10.4</v>
@@ -4321,28 +4321,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M37">
-        <v>2.117998698208183</v>
+        <v>2.178512946728417</v>
       </c>
       <c r="N37">
-        <v>4.816001301791816</v>
+        <v>4.755487053271583</v>
       </c>
       <c r="O37">
-        <v>1.204000325447954</v>
+        <v>1.188871763317896</v>
       </c>
       <c r="P37">
-        <v>3.612000976343862</v>
+        <v>3.566615289953687</v>
       </c>
       <c r="Q37">
-        <v>7.942000976343863</v>
+        <v>7.896615289953687</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1144740776158497</v>
+        <v>0.1153560221057793</v>
       </c>
       <c r="T37">
-        <v>1.338585595726359</v>
+        <v>1.355776335397503</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.273845260559475</v>
+        <v>3.182905114432824</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09113485414769876</v>
+        <v>0.09103530784509518</v>
       </c>
       <c r="C38">
-        <v>62.75020304403026</v>
+        <v>61.90196926912468</v>
       </c>
       <c r="D38">
-        <v>86.33636445945017</v>
+        <v>86.43219072386181</v>
       </c>
       <c r="E38">
-        <v>26.98015748369794</v>
+        <v>27.92421752301516</v>
       </c>
       <c r="F38">
-        <v>33.98616141541991</v>
+        <v>34.93022145473714</v>
       </c>
       <c r="G38">
         <v>10.4</v>
@@ -4403,28 +4403,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M38">
-        <v>2.178512946728417</v>
+        <v>2.239027195248651</v>
       </c>
       <c r="N38">
-        <v>4.755487053271583</v>
+        <v>4.694972804751348</v>
       </c>
       <c r="O38">
-        <v>1.188871763317896</v>
+        <v>1.173743201187837</v>
       </c>
       <c r="P38">
-        <v>3.566615289953687</v>
+        <v>3.521229603563511</v>
       </c>
       <c r="Q38">
-        <v>7.896615289953687</v>
+        <v>7.851229603563511</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1153560221057793</v>
+        <v>0.1162659648334844</v>
       </c>
       <c r="T38">
-        <v>1.355776335397503</v>
+        <v>1.373512812835984</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.182905114432824</v>
+        <v>3.096880651880585</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09103530784509518</v>
+        <v>0.09093576154249164</v>
       </c>
       <c r="C39">
-        <v>61.90196926912468</v>
+        <v>61.05394844912738</v>
       </c>
       <c r="D39">
-        <v>86.43219072386181</v>
+        <v>86.52822994318173</v>
       </c>
       <c r="E39">
-        <v>27.92421752301516</v>
+        <v>28.86827756233238</v>
       </c>
       <c r="F39">
-        <v>34.93022145473714</v>
+        <v>35.87428149405435</v>
       </c>
       <c r="G39">
         <v>10.4</v>
@@ -4485,28 +4485,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M39">
-        <v>2.239027195248651</v>
+        <v>2.299541443768884</v>
       </c>
       <c r="N39">
-        <v>4.694972804751348</v>
+        <v>4.634458556231115</v>
       </c>
       <c r="O39">
-        <v>1.173743201187837</v>
+        <v>1.158614639057779</v>
       </c>
       <c r="P39">
-        <v>3.521229603563511</v>
+        <v>3.475843917173336</v>
       </c>
       <c r="Q39">
-        <v>7.851229603563511</v>
+        <v>7.805843917173336</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1162659648334844</v>
+        <v>0.1172052605524058</v>
       </c>
       <c r="T39">
-        <v>1.373512812835984</v>
+        <v>1.391821434707965</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.096880651880585</v>
+        <v>3.01538379262057</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09093576154249164</v>
+        <v>0.09311771523988806</v>
       </c>
       <c r="C40">
-        <v>61.05394844912738</v>
+        <v>58.05257386117442</v>
       </c>
       <c r="D40">
-        <v>86.52822994318173</v>
+        <v>84.47091539454598</v>
       </c>
       <c r="E40">
-        <v>28.86827756233238</v>
+        <v>29.8123376016496</v>
       </c>
       <c r="F40">
-        <v>35.87428149405435</v>
+        <v>36.81834153337157</v>
       </c>
       <c r="G40">
         <v>10.4</v>
@@ -4567,45 +4567,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M40">
-        <v>2.299541443768884</v>
+        <v>2.647238756249416</v>
       </c>
       <c r="N40">
-        <v>4.634458556231115</v>
+        <v>4.286761243750583</v>
       </c>
       <c r="O40">
-        <v>1.158614639057779</v>
+        <v>1.071690310937646</v>
       </c>
       <c r="P40">
-        <v>3.475843917173336</v>
+        <v>3.215070932812937</v>
       </c>
       <c r="Q40">
-        <v>7.805843917173336</v>
+        <v>7.545070932812937</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1172052605524058</v>
+        <v>0.1181753528522755</v>
       </c>
       <c r="T40">
-        <v>1.391821434707965</v>
+        <v>1.410730339264272</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.01538379262057</v>
+        <v>2.619333063038117</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09311771523988806</v>
+        <v>0.09307666893728449</v>
       </c>
       <c r="C41">
-        <v>58.05257386117442</v>
+        <v>57.14631217528051</v>
       </c>
       <c r="D41">
-        <v>84.47091539454598</v>
+        <v>84.5087137479693</v>
       </c>
       <c r="E41">
-        <v>29.8123376016496</v>
+        <v>30.75639764096682</v>
       </c>
       <c r="F41">
-        <v>36.81834153337157</v>
+        <v>37.76240157268879</v>
       </c>
       <c r="G41">
         <v>10.4</v>
@@ -4649,28 +4649,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M41">
-        <v>2.647238756249416</v>
+        <v>2.715116673076325</v>
       </c>
       <c r="N41">
-        <v>4.286761243750583</v>
+        <v>4.218883326923675</v>
       </c>
       <c r="O41">
-        <v>1.071690310937646</v>
+        <v>1.054720831730919</v>
       </c>
       <c r="P41">
-        <v>3.215070932812937</v>
+        <v>3.164162495192756</v>
       </c>
       <c r="Q41">
-        <v>7.545070932812937</v>
+        <v>7.494162495192756</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1181753528522755</v>
+        <v>0.1191777815621408</v>
       </c>
       <c r="T41">
-        <v>1.410730339264272</v>
+        <v>1.430269540639124</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.619333063038117</v>
+        <v>2.553849736462164</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09307666893728449</v>
+        <v>0.09423487263468092</v>
       </c>
       <c r="C42">
-        <v>57.14631217528051</v>
+        <v>55.14852329195187</v>
       </c>
       <c r="D42">
-        <v>84.5087137479693</v>
+        <v>83.45498490395788</v>
       </c>
       <c r="E42">
-        <v>30.75639764096682</v>
+        <v>31.70045768028404</v>
       </c>
       <c r="F42">
-        <v>37.76240157268879</v>
+        <v>38.70646161200602</v>
       </c>
       <c r="G42">
         <v>10.4</v>
@@ -4731,45 +4731,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M42">
-        <v>2.715116673076325</v>
+        <v>2.933949790190056</v>
       </c>
       <c r="N42">
-        <v>4.218883326923675</v>
+        <v>4.000050209809944</v>
       </c>
       <c r="O42">
-        <v>1.054720831730919</v>
+        <v>1.000012552452486</v>
       </c>
       <c r="P42">
-        <v>3.164162495192756</v>
+        <v>3.000037657357458</v>
       </c>
       <c r="Q42">
-        <v>7.494162495192756</v>
+        <v>7.330037657357458</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1191777815621408</v>
+        <v>0.1202141909062389</v>
       </c>
       <c r="T42">
-        <v>1.430269540639124</v>
+        <v>1.450471087823292</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.553849736462164</v>
+        <v>2.363366961215388</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09423487263468092</v>
+        <v>0.09422307633207735</v>
       </c>
       <c r="C43">
-        <v>55.14852329195187</v>
+        <v>54.21506300634079</v>
       </c>
       <c r="D43">
-        <v>83.45498490395788</v>
+        <v>83.46558465766402</v>
       </c>
       <c r="E43">
-        <v>31.70045768028404</v>
+        <v>32.64451771960126</v>
       </c>
       <c r="F43">
-        <v>38.70646161200602</v>
+        <v>39.65052165132324</v>
       </c>
       <c r="G43">
         <v>10.4</v>
@@ -4813,28 +4813,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M43">
-        <v>2.933949790190056</v>
+        <v>3.005509541170302</v>
       </c>
       <c r="N43">
-        <v>4.000050209809944</v>
+        <v>3.928490458829697</v>
       </c>
       <c r="O43">
-        <v>1.000012552452486</v>
+        <v>0.9821226147074243</v>
       </c>
       <c r="P43">
-        <v>3.000037657357458</v>
+        <v>2.946367844122273</v>
       </c>
       <c r="Q43">
-        <v>7.330037657357458</v>
+        <v>7.276367844122273</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1202141909062389</v>
+        <v>0.1212863385035816</v>
       </c>
       <c r="T43">
-        <v>1.450471087823292</v>
+        <v>1.471369240082777</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.363366961215388</v>
+        <v>2.307096319281688</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09422307633207735</v>
+        <v>0.09421128002947379</v>
       </c>
       <c r="C44">
-        <v>54.2150630063408</v>
+        <v>53.28160541365575</v>
       </c>
       <c r="D44">
-        <v>83.46558465766402</v>
+        <v>83.4761871042962</v>
       </c>
       <c r="E44">
-        <v>32.64451771960125</v>
+        <v>33.58857775891848</v>
       </c>
       <c r="F44">
-        <v>39.65052165132323</v>
+        <v>40.59458169064045</v>
       </c>
       <c r="G44">
         <v>10.4</v>
@@ -4895,28 +4895,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M44">
-        <v>3.005509541170301</v>
+        <v>3.077069292150547</v>
       </c>
       <c r="N44">
-        <v>3.928490458829698</v>
+        <v>3.856930707849453</v>
       </c>
       <c r="O44">
-        <v>0.9821226147074246</v>
+        <v>0.9642326769623631</v>
       </c>
       <c r="P44">
-        <v>2.946367844122274</v>
+        <v>2.89269803088709</v>
       </c>
       <c r="Q44">
-        <v>7.276367844122274</v>
+        <v>7.22269803088709</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1212863385035816</v>
+        <v>0.1223961053148663</v>
       </c>
       <c r="T44">
-        <v>1.471369240082777</v>
+        <v>1.493000660842594</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.307096319281689</v>
+        <v>2.253442916507696</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09421128002947379</v>
+        <v>0.09419948372687023</v>
       </c>
       <c r="C45">
-        <v>53.28160541365575</v>
+        <v>52.34815051492311</v>
       </c>
       <c r="D45">
-        <v>83.4761871042962</v>
+        <v>83.48679224488077</v>
       </c>
       <c r="E45">
-        <v>33.58857775891848</v>
+        <v>34.5326377982357</v>
       </c>
       <c r="F45">
-        <v>40.59458169064045</v>
+        <v>41.53864172995767</v>
       </c>
       <c r="G45">
         <v>10.4</v>
@@ -4977,28 +4977,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M45">
-        <v>3.077069292150547</v>
+        <v>3.148629043130792</v>
       </c>
       <c r="N45">
-        <v>3.856930707849453</v>
+        <v>3.785370956869207</v>
       </c>
       <c r="O45">
-        <v>0.9642326769623631</v>
+        <v>0.9463427392173018</v>
       </c>
       <c r="P45">
-        <v>2.89269803088709</v>
+        <v>2.839028217651905</v>
       </c>
       <c r="Q45">
-        <v>7.22269803088709</v>
+        <v>7.169028217651905</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1223961053148663</v>
+        <v>0.1235455066551254</v>
       </c>
       <c r="T45">
-        <v>1.493000660842594</v>
+        <v>1.515404632343834</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.253442916507696</v>
+        <v>2.202228304768885</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09419948372687023</v>
+        <v>0.09418768742426667</v>
       </c>
       <c r="C46">
-        <v>52.34815051492311</v>
+        <v>51.41469831116973</v>
       </c>
       <c r="D46">
-        <v>83.48679224488077</v>
+        <v>83.49740008044462</v>
       </c>
       <c r="E46">
-        <v>34.5326377982357</v>
+        <v>35.47669783755292</v>
       </c>
       <c r="F46">
-        <v>41.53864172995767</v>
+        <v>42.4827017692749</v>
       </c>
       <c r="G46">
         <v>10.4</v>
@@ -5059,28 +5059,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M46">
-        <v>3.148629043130792</v>
+        <v>3.220188794111038</v>
       </c>
       <c r="N46">
-        <v>3.785370956869207</v>
+        <v>3.713811205888962</v>
       </c>
       <c r="O46">
-        <v>0.9463427392173018</v>
+        <v>0.9284528014722404</v>
       </c>
       <c r="P46">
-        <v>2.839028217651905</v>
+        <v>2.785358404416721</v>
       </c>
       <c r="Q46">
-        <v>7.169028217651905</v>
+        <v>7.115358404416721</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1235455066551254</v>
+        <v>0.1247367044077576</v>
       </c>
       <c r="T46">
-        <v>1.515404632343834</v>
+        <v>1.538623293717845</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.202228304768885</v>
+        <v>2.153289897996243</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09418768742426667</v>
+        <v>0.09417589112166309</v>
       </c>
       <c r="C47">
-        <v>51.41469831116973</v>
+        <v>50.48124880342306</v>
       </c>
       <c r="D47">
-        <v>83.49740008044462</v>
+        <v>83.50801061201517</v>
       </c>
       <c r="E47">
-        <v>35.47669783755292</v>
+        <v>36.42075787687013</v>
       </c>
       <c r="F47">
-        <v>42.4827017692749</v>
+        <v>43.42676180859211</v>
       </c>
       <c r="G47">
         <v>10.4</v>
@@ -5141,28 +5141,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M47">
-        <v>3.220188794111038</v>
+        <v>3.291748545091282</v>
       </c>
       <c r="N47">
-        <v>3.713811205888962</v>
+        <v>3.642251454908717</v>
       </c>
       <c r="O47">
-        <v>0.9284528014722404</v>
+        <v>0.9105628637271792</v>
       </c>
       <c r="P47">
-        <v>2.785358404416721</v>
+        <v>2.731688591181538</v>
       </c>
       <c r="Q47">
-        <v>7.115358404416721</v>
+        <v>7.061688591181538</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1247367044077576</v>
+        <v>0.1259720205956724</v>
       </c>
       <c r="T47">
-        <v>1.538623293717845</v>
+        <v>1.562701905513117</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.153289897996243</v>
+        <v>2.106479248039803</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09417589112166309</v>
+        <v>0.09416409481905953</v>
       </c>
       <c r="C48">
-        <v>50.48124880342306</v>
+        <v>49.54780199271098</v>
       </c>
       <c r="D48">
-        <v>83.50801061201517</v>
+        <v>83.51862384062031</v>
       </c>
       <c r="E48">
-        <v>36.42075787687013</v>
+        <v>37.36481791618736</v>
       </c>
       <c r="F48">
-        <v>43.42676180859211</v>
+        <v>44.37082184790933</v>
       </c>
       <c r="G48">
         <v>10.4</v>
@@ -5223,28 +5223,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M48">
-        <v>3.291748545091282</v>
+        <v>3.363308296071528</v>
       </c>
       <c r="N48">
-        <v>3.642251454908717</v>
+        <v>3.570691703928472</v>
       </c>
       <c r="O48">
-        <v>0.9105628637271792</v>
+        <v>0.8926729259821179</v>
       </c>
       <c r="P48">
-        <v>2.731688591181538</v>
+        <v>2.678018777946354</v>
       </c>
       <c r="Q48">
-        <v>7.061688591181538</v>
+        <v>7.008018777946354</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1259720205956724</v>
+        <v>0.1272539524887915</v>
       </c>
       <c r="T48">
-        <v>1.562701905513117</v>
+        <v>1.587689144168587</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.106479248039803</v>
+        <v>2.0616605406347</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09416409481905953</v>
+        <v>0.09415229851645596</v>
       </c>
       <c r="C49">
-        <v>49.54780199271098</v>
+        <v>48.61435788006195</v>
       </c>
       <c r="D49">
-        <v>83.51862384062031</v>
+        <v>83.5292397672885</v>
       </c>
       <c r="E49">
-        <v>37.36481791618736</v>
+        <v>38.30887795550458</v>
       </c>
       <c r="F49">
-        <v>44.37082184790933</v>
+        <v>45.31488188722656</v>
       </c>
       <c r="G49">
         <v>10.4</v>
@@ -5305,28 +5305,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M49">
-        <v>3.363308296071528</v>
+        <v>3.434868047051773</v>
       </c>
       <c r="N49">
-        <v>3.570691703928472</v>
+        <v>3.499131952948226</v>
       </c>
       <c r="O49">
-        <v>0.8926729259821179</v>
+        <v>0.8747829882370566</v>
       </c>
       <c r="P49">
-        <v>2.678018777946354</v>
+        <v>2.62434896471117</v>
       </c>
       <c r="Q49">
-        <v>7.008018777946354</v>
+        <v>6.95434896471117</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1272539524887915</v>
+        <v>0.128585189454723</v>
       </c>
       <c r="T49">
-        <v>1.587689144168587</v>
+        <v>1.613637430464653</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.0616605406347</v>
+        <v>2.018709279371477</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09415229851645596</v>
+        <v>0.09935900221385238</v>
       </c>
       <c r="C50">
-        <v>48.61435788006196</v>
+        <v>43.23294971776255</v>
       </c>
       <c r="D50">
-        <v>83.5292397672885</v>
+        <v>79.09189164430632</v>
       </c>
       <c r="E50">
-        <v>38.30887795550457</v>
+        <v>39.25293799482179</v>
       </c>
       <c r="F50">
-        <v>45.31488188722655</v>
+        <v>46.25894192654377</v>
       </c>
       <c r="G50">
         <v>10.4</v>
@@ -5387,45 +5387,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M50">
-        <v>3.434868047051773</v>
+        <v>4.163304773388939</v>
       </c>
       <c r="N50">
-        <v>3.499131952948227</v>
+        <v>2.77069522661106</v>
       </c>
       <c r="O50">
-        <v>0.8747829882370567</v>
+        <v>0.6926738066527651</v>
       </c>
       <c r="P50">
-        <v>2.62434896471117</v>
+        <v>2.078021419958295</v>
       </c>
       <c r="Q50">
-        <v>6.95434896471117</v>
+        <v>6.408021419958295</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.128585189454723</v>
+        <v>0.1299686317918674</v>
       </c>
       <c r="T50">
-        <v>1.613637430464653</v>
+        <v>1.640603296615465</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.018709279371478</v>
+        <v>1.6655038190624</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09935900221385238</v>
+        <v>0.09945370591124882</v>
       </c>
       <c r="C51">
-        <v>43.23294971776255</v>
+        <v>42.21254099138427</v>
       </c>
       <c r="D51">
-        <v>79.09189164430632</v>
+        <v>79.01554295724526</v>
       </c>
       <c r="E51">
-        <v>39.25293799482179</v>
+        <v>40.19699803413901</v>
       </c>
       <c r="F51">
-        <v>46.25894192654377</v>
+        <v>47.20300196586099</v>
       </c>
       <c r="G51">
         <v>10.4</v>
@@ -5469,28 +5469,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M51">
-        <v>4.163304773388939</v>
+        <v>4.248270176927489</v>
       </c>
       <c r="N51">
-        <v>2.77069522661106</v>
+        <v>2.68572982307251</v>
       </c>
       <c r="O51">
-        <v>0.6926738066527651</v>
+        <v>0.6714324557681275</v>
       </c>
       <c r="P51">
-        <v>2.078021419958295</v>
+        <v>2.014297367304382</v>
       </c>
       <c r="Q51">
-        <v>6.408021419958295</v>
+        <v>6.344297367304383</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1299686317918674</v>
+        <v>0.1314074118224976</v>
       </c>
       <c r="T51">
-        <v>1.640603296615465</v>
+        <v>1.668647797412311</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.6655038190624</v>
+        <v>1.632193742681152</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09945370591124882</v>
+        <v>0.09954840960864525</v>
       </c>
       <c r="C52">
-        <v>42.21254099138427</v>
+        <v>41.19227952410867</v>
       </c>
       <c r="D52">
-        <v>79.01554295724526</v>
+        <v>78.93934152928688</v>
       </c>
       <c r="E52">
-        <v>40.19699803413901</v>
+        <v>41.14105807345624</v>
       </c>
       <c r="F52">
-        <v>47.20300196586099</v>
+        <v>48.14706200517821</v>
       </c>
       <c r="G52">
         <v>10.4</v>
@@ -5551,28 +5551,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M52">
-        <v>4.248270176927489</v>
+        <v>4.333235580466039</v>
       </c>
       <c r="N52">
-        <v>2.68572982307251</v>
+        <v>2.60076441953396</v>
       </c>
       <c r="O52">
-        <v>0.6714324557681275</v>
+        <v>0.6501911048834901</v>
       </c>
       <c r="P52">
-        <v>2.014297367304382</v>
+        <v>1.95057331465047</v>
       </c>
       <c r="Q52">
-        <v>6.344297367304383</v>
+        <v>6.280573314650471</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1314074118224976</v>
+        <v>0.1329049175686638</v>
       </c>
       <c r="T52">
-        <v>1.668647797412311</v>
+        <v>1.697836971711069</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.632193742681152</v>
+        <v>1.600189943805051</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09954840960864525</v>
+        <v>0.09964311330604167</v>
       </c>
       <c r="C53">
-        <v>41.19227952410867</v>
+        <v>40.17216489030271</v>
       </c>
       <c r="D53">
-        <v>78.93934152928688</v>
+        <v>78.86328693479814</v>
       </c>
       <c r="E53">
-        <v>41.14105807345624</v>
+        <v>42.08511811277346</v>
       </c>
       <c r="F53">
-        <v>48.14706200517821</v>
+        <v>49.09112204449544</v>
       </c>
       <c r="G53">
         <v>10.4</v>
@@ -5633,28 +5633,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M53">
-        <v>4.333235580466039</v>
+        <v>4.418200984004589</v>
       </c>
       <c r="N53">
-        <v>2.60076441953396</v>
+        <v>2.515799015995411</v>
       </c>
       <c r="O53">
-        <v>0.6501911048834901</v>
+        <v>0.6289497539988527</v>
       </c>
       <c r="P53">
-        <v>1.95057331465047</v>
+        <v>1.886849261996558</v>
       </c>
       <c r="Q53">
-        <v>6.280573314650471</v>
+        <v>6.216849261996558</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1329049175686638</v>
+        <v>0.1344648193875868</v>
       </c>
       <c r="T53">
-        <v>1.697836971711069</v>
+        <v>1.728242361605608</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.600189943805051</v>
+        <v>1.569417060270339</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09964311330604167</v>
+        <v>0.09973781700343812</v>
       </c>
       <c r="C54">
-        <v>40.17216489030271</v>
+        <v>39.15219666597199</v>
       </c>
       <c r="D54">
-        <v>78.86328693479814</v>
+        <v>78.78737874978464</v>
       </c>
       <c r="E54">
-        <v>42.08511811277346</v>
+        <v>43.02917815209068</v>
       </c>
       <c r="F54">
-        <v>49.09112204449544</v>
+        <v>50.03518208381266</v>
       </c>
       <c r="G54">
         <v>10.4</v>
@@ -5715,28 +5715,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M54">
-        <v>4.418200984004589</v>
+        <v>4.503166387543139</v>
       </c>
       <c r="N54">
-        <v>2.515799015995411</v>
+        <v>2.43083361245686</v>
       </c>
       <c r="O54">
-        <v>0.6289497539988527</v>
+        <v>0.607708403114215</v>
       </c>
       <c r="P54">
-        <v>1.886849261996558</v>
+        <v>1.823125209342645</v>
       </c>
       <c r="Q54">
-        <v>6.216849261996558</v>
+        <v>6.153125209342646</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1344648193875868</v>
+        <v>0.1360911000073151</v>
       </c>
       <c r="T54">
-        <v>1.728242361605608</v>
+        <v>1.759941597878638</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.569417060270339</v>
+        <v>1.539805417623728</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09973781700343812</v>
+        <v>0.09983252070083454</v>
       </c>
       <c r="C55">
-        <v>39.15219666597199</v>
+        <v>38.13237442875312</v>
       </c>
       <c r="D55">
-        <v>78.78737874978464</v>
+        <v>78.71161655188298</v>
       </c>
       <c r="E55">
-        <v>43.02917815209068</v>
+        <v>43.97323819140789</v>
       </c>
       <c r="F55">
-        <v>50.03518208381266</v>
+        <v>50.97924212312987</v>
       </c>
       <c r="G55">
         <v>10.4</v>
@@ -5797,28 +5797,28 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M55">
-        <v>4.503166387543139</v>
+        <v>4.588131791081688</v>
       </c>
       <c r="N55">
-        <v>2.43083361245686</v>
+        <v>2.345868208918311</v>
       </c>
       <c r="O55">
-        <v>0.607708403114215</v>
+        <v>0.5864670522295778</v>
       </c>
       <c r="P55">
-        <v>1.823125209342645</v>
+        <v>1.759401156688734</v>
       </c>
       <c r="Q55">
-        <v>6.153125209342646</v>
+        <v>6.089401156688734</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1360911000073151</v>
+        <v>0.1377880884800751</v>
       </c>
       <c r="T55">
-        <v>1.759941597878638</v>
+        <v>1.793019061815713</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.539805417623728</v>
+        <v>1.511290502482548</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09983252070083454</v>
+        <v>0.1257874676666346</v>
       </c>
       <c r="C56">
-        <v>38.13237442875312</v>
+        <v>20.77113957885603</v>
       </c>
       <c r="D56">
-        <v>78.71161655188298</v>
+        <v>62.29444174130312</v>
       </c>
       <c r="E56">
-        <v>43.97323819140789</v>
+        <v>44.91729823072512</v>
       </c>
       <c r="F56">
-        <v>50.97924212312987</v>
+        <v>51.92330216244709</v>
       </c>
       <c r="G56">
         <v>10.4</v>
@@ -5879,45 +5879,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M56">
-        <v>4.588131791081688</v>
+        <v>7.622340757447234</v>
       </c>
       <c r="N56">
-        <v>2.345868208918311</v>
+        <v>-0.6883407574472349</v>
       </c>
       <c r="O56">
-        <v>0.5864670522295778</v>
+        <v>-0.1720851893618087</v>
       </c>
       <c r="P56">
-        <v>1.759401156688734</v>
+        <v>-0.5162555680854262</v>
       </c>
       <c r="Q56">
-        <v>6.089401156688734</v>
+        <v>3.813744431914574</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1377880884800751</v>
+        <v>0.1409103272706613</v>
       </c>
       <c r="T56">
-        <v>1.793019061815713</v>
+        <v>1.853877307264243</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.25</v>
+        <v>0.2274235769774952</v>
       </c>
       <c r="W56">
-        <v>0.0675</v>
+        <v>0.1134142188997037</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.511290502482548</v>
+        <v>0.9096943079099806</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1257874676666346</v>
+        <v>0.1267974676666346</v>
       </c>
       <c r="C57">
-        <v>20.77113957885603</v>
+        <v>19.32554660420467</v>
       </c>
       <c r="D57">
-        <v>62.29444174130312</v>
+        <v>61.79290880596898</v>
       </c>
       <c r="E57">
-        <v>44.91729823072512</v>
+        <v>45.86135827004234</v>
       </c>
       <c r="F57">
-        <v>51.92330216244709</v>
+        <v>52.86736220176432</v>
       </c>
       <c r="G57">
         <v>10.4</v>
@@ -5961,37 +5961,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M57">
-        <v>7.622340757447234</v>
+        <v>7.760928771219002</v>
       </c>
       <c r="N57">
-        <v>-0.6883407574472349</v>
+        <v>-0.826928771219003</v>
       </c>
       <c r="O57">
-        <v>-0.1720851893618087</v>
+        <v>-0.2067321928047507</v>
       </c>
       <c r="P57">
-        <v>-0.5162555680854262</v>
+        <v>-0.6201965784142522</v>
       </c>
       <c r="Q57">
-        <v>3.813744431914574</v>
+        <v>3.709803421585748</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1409103272706613</v>
+        <v>0.1430719256177218</v>
       </c>
       <c r="T57">
-        <v>1.853877307264243</v>
+        <v>1.89601088242934</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2274235769774952</v>
+        <v>0.2233624416743256</v>
       </c>
       <c r="W57">
-        <v>0.1134142188997037</v>
+        <v>0.114010393562209</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9096943079099806</v>
+        <v>0.8934497666973024</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1267974676666346</v>
+        <v>0.1278074676666346</v>
       </c>
       <c r="C58">
-        <v>19.32554660420467</v>
+        <v>17.8879648209241</v>
       </c>
       <c r="D58">
-        <v>61.79290880596898</v>
+        <v>61.29938706200564</v>
       </c>
       <c r="E58">
-        <v>45.86135827004234</v>
+        <v>46.80541830935956</v>
       </c>
       <c r="F58">
-        <v>52.86736220176432</v>
+        <v>53.81142224108154</v>
       </c>
       <c r="G58">
         <v>10.4</v>
@@ -6043,37 +6043,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M58">
-        <v>7.760928771219002</v>
+        <v>7.89951678499077</v>
       </c>
       <c r="N58">
-        <v>-0.826928771219003</v>
+        <v>-0.9655167849907711</v>
       </c>
       <c r="O58">
-        <v>-0.2067321928047507</v>
+        <v>-0.2413791962476928</v>
       </c>
       <c r="P58">
-        <v>-0.6201965784142522</v>
+        <v>-0.7241375887430783</v>
       </c>
       <c r="Q58">
-        <v>3.709803421585748</v>
+        <v>3.605862411256922</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1430719256177218</v>
+        <v>0.1453340634227851</v>
       </c>
       <c r="T58">
-        <v>1.89601088242934</v>
+        <v>1.940104158764906</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2233624416743256</v>
+        <v>0.2194438023467059</v>
       </c>
       <c r="W58">
-        <v>0.114010393562209</v>
+        <v>0.1145856498155036</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8934497666973024</v>
+        <v>0.8777752093868234</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1278074676666346</v>
+        <v>0.1288174676666346</v>
       </c>
       <c r="C59">
-        <v>17.8879648209241</v>
+        <v>16.45820380083752</v>
       </c>
       <c r="D59">
-        <v>61.29938706200564</v>
+        <v>60.81368608123628</v>
       </c>
       <c r="E59">
-        <v>46.80541830935956</v>
+        <v>47.74947834867678</v>
       </c>
       <c r="F59">
-        <v>53.81142224108154</v>
+        <v>54.75548228039876</v>
       </c>
       <c r="G59">
         <v>10.4</v>
@@ -6125,37 +6125,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M59">
-        <v>7.89951678499077</v>
+        <v>8.038104798762539</v>
       </c>
       <c r="N59">
-        <v>-0.9655167849907711</v>
+        <v>-1.10410479876254</v>
       </c>
       <c r="O59">
-        <v>-0.2413791962476928</v>
+        <v>-0.276026199690635</v>
       </c>
       <c r="P59">
-        <v>-0.7241375887430783</v>
+        <v>-0.8280785990719051</v>
       </c>
       <c r="Q59">
-        <v>3.605862411256922</v>
+        <v>3.501921400928095</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1453340634227851</v>
+        <v>0.1477039220757085</v>
       </c>
       <c r="T59">
-        <v>1.940104158764906</v>
+        <v>1.986297114925975</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2194438023467059</v>
+        <v>0.2156602885131419</v>
       </c>
       <c r="W59">
-        <v>0.1145856498155036</v>
+        <v>0.1151410696462708</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8777752093868234</v>
+        <v>0.8626411540525677</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1288174676666346</v>
+        <v>0.1298274676666346</v>
       </c>
       <c r="C60">
-        <v>16.45820380083754</v>
+        <v>15.03607910369531</v>
       </c>
       <c r="D60">
-        <v>60.81368608123629</v>
+        <v>60.33562142341128</v>
       </c>
       <c r="E60">
-        <v>47.74947834867677</v>
+        <v>48.69353838799399</v>
       </c>
       <c r="F60">
-        <v>54.75548228039874</v>
+        <v>55.69954231971597</v>
       </c>
       <c r="G60">
         <v>10.4</v>
@@ -6207,37 +6207,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M60">
-        <v>8.038104798762536</v>
+        <v>8.176692812534304</v>
       </c>
       <c r="N60">
-        <v>-1.104104798762537</v>
+        <v>-1.242692812534305</v>
       </c>
       <c r="O60">
-        <v>-0.2760261996906341</v>
+        <v>-0.3106732031335762</v>
       </c>
       <c r="P60">
-        <v>-0.8280785990719024</v>
+        <v>-0.9320196094007285</v>
       </c>
       <c r="Q60">
-        <v>3.501921400928098</v>
+        <v>3.397980390599272</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1477039220757085</v>
+        <v>0.1501893835897502</v>
       </c>
       <c r="T60">
-        <v>1.986297114925974</v>
+        <v>2.03474338602173</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.215660288513142</v>
+        <v>0.2120050293858006</v>
       </c>
       <c r="W60">
-        <v>0.1151410696462708</v>
+        <v>0.1156776616861645</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.862641154052568</v>
+        <v>0.8480201175432025</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1298274676666346</v>
+        <v>0.1308374676666346</v>
       </c>
       <c r="C61">
-        <v>15.03607910369531</v>
+        <v>13.62141204365125</v>
       </c>
       <c r="D61">
-        <v>60.33562142341128</v>
+        <v>59.86501440268444</v>
       </c>
       <c r="E61">
-        <v>48.69353838799399</v>
+        <v>49.63759842731121</v>
       </c>
       <c r="F61">
-        <v>55.69954231971597</v>
+        <v>56.64360235903319</v>
       </c>
       <c r="G61">
         <v>10.4</v>
@@ -6289,37 +6289,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M61">
-        <v>8.176692812534304</v>
+        <v>8.315280826306072</v>
       </c>
       <c r="N61">
-        <v>-1.242692812534305</v>
+        <v>-1.381280826306073</v>
       </c>
       <c r="O61">
-        <v>-0.3106732031335762</v>
+        <v>-0.3453202065765182</v>
       </c>
       <c r="P61">
-        <v>-0.9320196094007285</v>
+        <v>-1.035960619729555</v>
       </c>
       <c r="Q61">
-        <v>3.397980390599272</v>
+        <v>3.294039380270446</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1501893835897502</v>
+        <v>0.152799118179494</v>
       </c>
       <c r="T61">
-        <v>2.03474338602173</v>
+        <v>2.085611970672274</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2120050293858006</v>
+        <v>0.2084716122293706</v>
       </c>
       <c r="W61">
-        <v>0.1156776616861645</v>
+        <v>0.1161963673247284</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8480201175432025</v>
+        <v>0.8338864489174824</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1308374676666346</v>
+        <v>0.1318474676666346</v>
       </c>
       <c r="C62">
-        <v>13.62141204365125</v>
+        <v>12.21402946658284</v>
       </c>
       <c r="D62">
-        <v>59.86501440268444</v>
+        <v>59.40169186493325</v>
       </c>
       <c r="E62">
-        <v>49.63759842731121</v>
+        <v>50.58165846662843</v>
       </c>
       <c r="F62">
-        <v>56.64360235903319</v>
+        <v>57.58766239835041</v>
       </c>
       <c r="G62">
         <v>10.4</v>
@@ -6371,37 +6371,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M62">
-        <v>8.315280826306072</v>
+        <v>8.453868840077842</v>
       </c>
       <c r="N62">
-        <v>-1.381280826306073</v>
+        <v>-1.519868840077843</v>
       </c>
       <c r="O62">
-        <v>-0.3453202065765182</v>
+        <v>-0.3799672100194607</v>
       </c>
       <c r="P62">
-        <v>-1.035960619729555</v>
+        <v>-1.139901630058382</v>
       </c>
       <c r="Q62">
-        <v>3.294039380270446</v>
+        <v>3.190098369941618</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.152799118179494</v>
+        <v>0.1555426853123015</v>
       </c>
       <c r="T62">
-        <v>2.085611970672274</v>
+        <v>2.139089200689511</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2084716122293706</v>
+        <v>0.2050540448157743</v>
       </c>
       <c r="W62">
-        <v>0.1161963673247284</v>
+        <v>0.1166980662210444</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8338864489174824</v>
+        <v>0.8202161792630973</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1318474676666346</v>
+        <v>0.1328574676666346</v>
       </c>
       <c r="C63">
-        <v>12.21402946658284</v>
+        <v>10.81376353767266</v>
       </c>
       <c r="D63">
-        <v>59.40169186493325</v>
+        <v>58.9454859753403</v>
       </c>
       <c r="E63">
-        <v>50.58165846662843</v>
+        <v>51.52571850594565</v>
       </c>
       <c r="F63">
-        <v>57.58766239835041</v>
+        <v>58.53172243766763</v>
       </c>
       <c r="G63">
         <v>10.4</v>
@@ -6453,37 +6453,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M63">
-        <v>8.453868840077842</v>
+        <v>8.59245685384961</v>
       </c>
       <c r="N63">
-        <v>-1.519868840077843</v>
+        <v>-1.658456853849611</v>
       </c>
       <c r="O63">
-        <v>-0.3799672100194607</v>
+        <v>-0.4146142134624027</v>
       </c>
       <c r="P63">
-        <v>-1.139901630058382</v>
+        <v>-1.243842640387208</v>
       </c>
       <c r="Q63">
-        <v>3.190098369941618</v>
+        <v>3.086157359612792</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1555426853123015</v>
+        <v>0.1584306507152568</v>
       </c>
       <c r="T63">
-        <v>2.139089200689511</v>
+        <v>2.195381021760288</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2050540448157743</v>
+        <v>0.2017467215122941</v>
       </c>
       <c r="W63">
-        <v>0.1166980662210444</v>
+        <v>0.1171835812819952</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8202161792630973</v>
+        <v>0.8069868860491763</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1328574676666346</v>
+        <v>0.1695329815289852</v>
       </c>
       <c r="C64">
-        <v>10.81376353767266</v>
+        <v>-2.984280788708077</v>
       </c>
       <c r="D64">
-        <v>58.9454859753403</v>
+        <v>46.09150168827677</v>
       </c>
       <c r="E64">
-        <v>51.52571850594565</v>
+        <v>52.46977854526287</v>
       </c>
       <c r="F64">
-        <v>58.53172243766763</v>
+        <v>59.47578247698485</v>
       </c>
       <c r="G64">
         <v>10.4</v>
@@ -6535,45 +6535,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M64">
-        <v>8.59245685384961</v>
+        <v>11.94273712137856</v>
       </c>
       <c r="N64">
-        <v>-1.658456853849611</v>
+        <v>-5.008737121378559</v>
       </c>
       <c r="O64">
-        <v>-0.4146142134624027</v>
+        <v>-1.25218428034464</v>
       </c>
       <c r="P64">
-        <v>-1.243842640387208</v>
+        <v>-3.756552841033919</v>
       </c>
       <c r="Q64">
-        <v>3.086157359612792</v>
+        <v>0.573447158966081</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1584306507152568</v>
+        <v>0.1659220571193194</v>
       </c>
       <c r="T64">
-        <v>2.195381021760288</v>
+        <v>2.341402476322875</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.2017467215122941</v>
+        <v>0.1451509802469721</v>
       </c>
       <c r="W64">
-        <v>0.1171835812819952</v>
+        <v>0.171653683166408</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8069868860491763</v>
+        <v>0.5806039209878885</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1695329815289852</v>
+        <v>0.1710829815289852</v>
       </c>
       <c r="C65">
-        <v>-2.984280788708077</v>
+        <v>-4.349241318080658</v>
       </c>
       <c r="D65">
-        <v>46.09150168827677</v>
+        <v>45.67060119822141</v>
       </c>
       <c r="E65">
-        <v>52.46977854526287</v>
+        <v>53.41383858458009</v>
       </c>
       <c r="F65">
-        <v>59.47578247698485</v>
+        <v>60.41984251630207</v>
       </c>
       <c r="G65">
         <v>10.4</v>
@@ -6617,37 +6617,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M65">
-        <v>11.94273712137856</v>
+        <v>12.13230437727346</v>
       </c>
       <c r="N65">
-        <v>-5.008737121378559</v>
+        <v>-5.198304377273457</v>
       </c>
       <c r="O65">
-        <v>-1.25218428034464</v>
+        <v>-1.299576094318364</v>
       </c>
       <c r="P65">
-        <v>-3.756552841033919</v>
+        <v>-3.898728282955093</v>
       </c>
       <c r="Q65">
-        <v>0.573447158966081</v>
+        <v>0.4312717170449072</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1659220571193194</v>
+        <v>0.1692587809281894</v>
       </c>
       <c r="T65">
-        <v>2.341402476322875</v>
+        <v>2.406441433998511</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1451509802469721</v>
+        <v>0.1428829961806132</v>
       </c>
       <c r="W65">
-        <v>0.171653683166408</v>
+        <v>0.1721090943669329</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5806039209878885</v>
+        <v>0.5715319847224527</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1710829815289852</v>
+        <v>0.1726329815289852</v>
       </c>
       <c r="C66">
-        <v>-4.349241318080658</v>
+        <v>-5.706584213693965</v>
       </c>
       <c r="D66">
-        <v>45.67060119822141</v>
+        <v>45.25731834192533</v>
       </c>
       <c r="E66">
-        <v>53.41383858458009</v>
+        <v>54.35789862389731</v>
       </c>
       <c r="F66">
-        <v>60.41984251630207</v>
+        <v>61.36390255561929</v>
       </c>
       <c r="G66">
         <v>10.4</v>
@@ -6699,37 +6699,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M66">
-        <v>12.13230437727346</v>
+        <v>12.32187163316835</v>
       </c>
       <c r="N66">
-        <v>-5.198304377273457</v>
+        <v>-5.387871633168354</v>
       </c>
       <c r="O66">
-        <v>-1.299576094318364</v>
+        <v>-1.346967908292088</v>
       </c>
       <c r="P66">
-        <v>-3.898728282955093</v>
+        <v>-4.040903724876266</v>
       </c>
       <c r="Q66">
-        <v>0.4312717170449072</v>
+        <v>0.2890962751237343</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1692587809281894</v>
+        <v>0.1727861746689948</v>
       </c>
       <c r="T66">
-        <v>2.406441433998511</v>
+        <v>2.475196903541326</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1428829961806132</v>
+        <v>0.140684796239373</v>
       </c>
       <c r="W66">
-        <v>0.1721090943669329</v>
+        <v>0.1725504929151339</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5715319847224527</v>
+        <v>0.562739184957492</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1726329815289852</v>
+        <v>0.1741829815289852</v>
       </c>
       <c r="C67">
-        <v>-5.706584213693965</v>
+        <v>-7.056514421648131</v>
       </c>
       <c r="D67">
-        <v>45.25731834192533</v>
+        <v>44.85144817328838</v>
       </c>
       <c r="E67">
-        <v>54.35789862389731</v>
+        <v>55.30195866321453</v>
       </c>
       <c r="F67">
-        <v>61.36390255561929</v>
+        <v>62.30796259493651</v>
       </c>
       <c r="G67">
         <v>10.4</v>
@@ -6781,37 +6781,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M67">
-        <v>12.32187163316835</v>
+        <v>12.51143888906325</v>
       </c>
       <c r="N67">
-        <v>-5.387871633168354</v>
+        <v>-5.577438889063252</v>
       </c>
       <c r="O67">
-        <v>-1.346967908292088</v>
+        <v>-1.394359722265813</v>
       </c>
       <c r="P67">
-        <v>-4.040903724876266</v>
+        <v>-4.183079166797439</v>
       </c>
       <c r="Q67">
-        <v>0.2890962751237343</v>
+        <v>0.1469208332025609</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1727861746689948</v>
+        <v>0.1765210621592593</v>
       </c>
       <c r="T67">
-        <v>2.475196903541326</v>
+        <v>2.547996812469012</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.140684796239373</v>
+        <v>0.1385532084175643</v>
       </c>
       <c r="W67">
-        <v>0.1725504929151339</v>
+        <v>0.1729785157497531</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.562739184957492</v>
+        <v>0.5542128336702572</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1741829815289852</v>
+        <v>0.1757329815289852</v>
       </c>
       <c r="C68">
-        <v>-7.056514421648131</v>
+        <v>-8.399229601516751</v>
       </c>
       <c r="D68">
-        <v>44.85144817328838</v>
+        <v>44.45279303273698</v>
       </c>
       <c r="E68">
-        <v>55.30195866321453</v>
+        <v>56.24601870253176</v>
       </c>
       <c r="F68">
-        <v>62.30796259493651</v>
+        <v>63.25202263425373</v>
       </c>
       <c r="G68">
         <v>10.4</v>
@@ -6863,37 +6863,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M68">
-        <v>12.51143888906325</v>
+        <v>12.70100614495815</v>
       </c>
       <c r="N68">
-        <v>-5.577438889063252</v>
+        <v>-5.767006144958151</v>
       </c>
       <c r="O68">
-        <v>-1.394359722265813</v>
+        <v>-1.441751536239538</v>
       </c>
       <c r="P68">
-        <v>-4.183079166797439</v>
+        <v>-4.325254608718613</v>
       </c>
       <c r="Q68">
-        <v>0.1469208332025609</v>
+        <v>0.004745391281387512</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1765210621592593</v>
+        <v>0.1804823064671157</v>
       </c>
       <c r="T68">
-        <v>2.547996812469012</v>
+        <v>2.625208837089285</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1385532084175643</v>
+        <v>0.1364852500829738</v>
       </c>
       <c r="W68">
-        <v>0.1729785157497531</v>
+        <v>0.1733937617833389</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5542128336702572</v>
+        <v>0.5459410003318952</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1757329815289852</v>
+        <v>0.1772829815289852</v>
       </c>
       <c r="C69">
-        <v>-8.399229601516751</v>
+        <v>-9.734920447319858</v>
       </c>
       <c r="D69">
-        <v>44.45279303273698</v>
+        <v>44.0611622262511</v>
       </c>
       <c r="E69">
-        <v>56.24601870253176</v>
+        <v>57.19007874184898</v>
       </c>
       <c r="F69">
-        <v>63.25202263425373</v>
+        <v>64.19608267357096</v>
       </c>
       <c r="G69">
         <v>10.4</v>
@@ -6945,37 +6945,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M69">
-        <v>12.70100614495815</v>
+        <v>12.89057340085305</v>
       </c>
       <c r="N69">
-        <v>-5.767006144958151</v>
+        <v>-5.956573400853049</v>
       </c>
       <c r="O69">
-        <v>-1.441751536239538</v>
+        <v>-1.489143350213262</v>
       </c>
       <c r="P69">
-        <v>-4.325254608718613</v>
+        <v>-4.467430050639787</v>
       </c>
       <c r="Q69">
-        <v>0.004745391281387512</v>
+        <v>-0.1374300506397867</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1804823064671157</v>
+        <v>0.1846911285442131</v>
       </c>
       <c r="T69">
-        <v>2.625208837089285</v>
+        <v>2.707246613248325</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1364852500829738</v>
+        <v>0.1344781140523418</v>
       </c>
       <c r="W69">
-        <v>0.1733937617833389</v>
+        <v>0.1737967946982898</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5459410003318952</v>
+        <v>0.5379124562093672</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1772829815289852</v>
+        <v>0.1788329815289852</v>
       </c>
       <c r="C70">
-        <v>-9.734920447319858</v>
+        <v>-11.06377099167818</v>
       </c>
       <c r="D70">
-        <v>44.0611622262511</v>
+        <v>43.67637172121</v>
       </c>
       <c r="E70">
-        <v>57.19007874184898</v>
+        <v>58.1341387811662</v>
       </c>
       <c r="F70">
-        <v>64.19608267357096</v>
+        <v>65.14014271288818</v>
       </c>
       <c r="G70">
         <v>10.4</v>
@@ -7027,37 +7027,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M70">
-        <v>12.89057340085305</v>
+        <v>13.08014065674795</v>
       </c>
       <c r="N70">
-        <v>-5.956573400853049</v>
+        <v>-6.146140656747948</v>
       </c>
       <c r="O70">
-        <v>-1.489143350213262</v>
+        <v>-1.536535164186987</v>
       </c>
       <c r="P70">
-        <v>-4.467430050639787</v>
+        <v>-4.609605492560961</v>
       </c>
       <c r="Q70">
-        <v>-0.1374300506397867</v>
+        <v>-0.279605492560961</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1846911285442131</v>
+        <v>0.1891714875295103</v>
       </c>
       <c r="T70">
-        <v>2.707246613248325</v>
+        <v>2.794577149159562</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1344781140523418</v>
+        <v>0.1325291558776702</v>
       </c>
       <c r="W70">
-        <v>0.1737967946982898</v>
+        <v>0.1741881454997638</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5379124562093672</v>
+        <v>0.5301166235106807</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1788329815289852</v>
+        <v>0.1803829815289852</v>
       </c>
       <c r="C71">
-        <v>-11.06377099167818</v>
+        <v>-12.3859588941683</v>
       </c>
       <c r="D71">
-        <v>43.67637172121</v>
+        <v>43.2982438580371</v>
       </c>
       <c r="E71">
-        <v>58.1341387811662</v>
+        <v>59.07819882048342</v>
       </c>
       <c r="F71">
-        <v>65.14014271288818</v>
+        <v>66.0842027522054</v>
       </c>
       <c r="G71">
         <v>10.4</v>
@@ -7109,37 +7109,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M71">
-        <v>13.08014065674795</v>
+        <v>13.26970791264285</v>
       </c>
       <c r="N71">
-        <v>-6.146140656747948</v>
+        <v>-6.335707912642846</v>
       </c>
       <c r="O71">
-        <v>-1.536535164186987</v>
+        <v>-1.583926978160711</v>
       </c>
       <c r="P71">
-        <v>-4.609605492560961</v>
+        <v>-4.751780934482134</v>
       </c>
       <c r="Q71">
-        <v>-0.279605492560961</v>
+        <v>-0.4217809344821344</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1891714875295103</v>
+        <v>0.1939505371138273</v>
       </c>
       <c r="T71">
-        <v>2.794577149159562</v>
+        <v>2.887729720798214</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1325291558776702</v>
+        <v>0.1306358822222749</v>
       </c>
       <c r="W71">
-        <v>0.1741881454997638</v>
+        <v>0.1745683148497672</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5301166235106807</v>
+        <v>0.5225435288890996</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1803829815289852</v>
+        <v>0.1819329815289852</v>
       </c>
       <c r="C72">
-        <v>-12.3859588941683</v>
+        <v>-13.70165571482768</v>
       </c>
       <c r="D72">
-        <v>43.2982438580371</v>
+        <v>42.92660707669494</v>
       </c>
       <c r="E72">
-        <v>59.07819882048342</v>
+        <v>60.02225885980064</v>
       </c>
       <c r="F72">
-        <v>66.0842027522054</v>
+        <v>67.02826279152262</v>
       </c>
       <c r="G72">
         <v>10.4</v>
@@ -7191,37 +7191,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M72">
-        <v>13.26970791264285</v>
+        <v>13.45927516853774</v>
       </c>
       <c r="N72">
-        <v>-6.335707912642846</v>
+        <v>-6.525275168537744</v>
       </c>
       <c r="O72">
-        <v>-1.583926978160711</v>
+        <v>-1.631318792134436</v>
       </c>
       <c r="P72">
-        <v>-4.751780934482134</v>
+        <v>-4.893956376403308</v>
       </c>
       <c r="Q72">
-        <v>-0.4217809344821344</v>
+        <v>-0.5639563764033078</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1939505371138273</v>
+        <v>0.1990591763246489</v>
       </c>
       <c r="T72">
-        <v>2.887729720798214</v>
+        <v>2.98730660772229</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1306358822222749</v>
+        <v>0.1287959402191443</v>
       </c>
       <c r="W72">
-        <v>0.1745683148497672</v>
+        <v>0.1749377752039958</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5225435288890996</v>
+        <v>0.515183760876577</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1819329815289852</v>
+        <v>0.1834829815289852</v>
       </c>
       <c r="C73">
-        <v>-13.70165571482765</v>
+        <v>-15.01102717369422</v>
       </c>
       <c r="D73">
-        <v>42.92660707669496</v>
+        <v>42.56129565714561</v>
       </c>
       <c r="E73">
-        <v>60.02225885980063</v>
+        <v>60.96631889911785</v>
       </c>
       <c r="F73">
-        <v>67.02826279152261</v>
+        <v>67.97232283083983</v>
       </c>
       <c r="G73">
         <v>10.4</v>
@@ -7273,37 +7273,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M73">
-        <v>13.45927516853774</v>
+        <v>13.64884242443264</v>
       </c>
       <c r="N73">
-        <v>-6.525275168537741</v>
+        <v>-6.714842424432639</v>
       </c>
       <c r="O73">
-        <v>-1.631318792134435</v>
+        <v>-1.67871060610816</v>
       </c>
       <c r="P73">
-        <v>-4.893956376403306</v>
+        <v>-5.036131818324479</v>
       </c>
       <c r="Q73">
-        <v>-0.563956376403306</v>
+        <v>-0.7061318183244794</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1990591763246489</v>
+        <v>0.2045327183362435</v>
       </c>
       <c r="T73">
-        <v>2.987306607722289</v>
+        <v>3.093996129426657</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1287959402191443</v>
+        <v>0.1270071077161006</v>
       </c>
       <c r="W73">
-        <v>0.1749377752039958</v>
+        <v>0.175296972770607</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5151837608765771</v>
+        <v>0.5080284308644024</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1834829815289852</v>
+        <v>0.1850329815289852</v>
       </c>
       <c r="C74">
-        <v>-15.01102717369422</v>
+        <v>-16.31423339720561</v>
       </c>
       <c r="D74">
-        <v>42.56129565714561</v>
+        <v>42.20214947295145</v>
       </c>
       <c r="E74">
-        <v>60.96631889911785</v>
+        <v>61.91037893843507</v>
       </c>
       <c r="F74">
-        <v>67.97232283083983</v>
+        <v>68.91638287015705</v>
       </c>
       <c r="G74">
         <v>10.4</v>
@@ -7355,37 +7355,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M74">
-        <v>13.64884242443264</v>
+        <v>13.83840968032754</v>
       </c>
       <c r="N74">
-        <v>-6.714842424432639</v>
+        <v>-6.904409680327538</v>
       </c>
       <c r="O74">
-        <v>-1.67871060610816</v>
+        <v>-1.726102420081884</v>
       </c>
       <c r="P74">
-        <v>-5.036131818324479</v>
+        <v>-5.178307260245653</v>
       </c>
       <c r="Q74">
-        <v>-0.7061318183244794</v>
+        <v>-0.8483072602456527</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2045327183362435</v>
+        <v>0.2104117079042525</v>
       </c>
       <c r="T74">
-        <v>3.093996129426657</v>
+        <v>3.208588578664681</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1270071077161006</v>
+        <v>0.1252672843227293</v>
       </c>
       <c r="W74">
-        <v>0.175296972770607</v>
+        <v>0.175646329307996</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5080284308644024</v>
+        <v>0.5010691372909174</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1850329815289852</v>
+        <v>0.213146966248047</v>
       </c>
       <c r="C75">
-        <v>-16.31423339720561</v>
+        <v>-22.86014663377033</v>
       </c>
       <c r="D75">
-        <v>42.20214947295145</v>
+        <v>36.60029627570395</v>
       </c>
       <c r="E75">
-        <v>61.91037893843507</v>
+        <v>62.8544389777523</v>
       </c>
       <c r="F75">
-        <v>68.91638287015705</v>
+        <v>69.86044290947427</v>
       </c>
       <c r="G75">
         <v>10.4</v>
@@ -7437,45 +7437,45 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M75">
-        <v>13.83840968032754</v>
+        <v>16.47309243805404</v>
       </c>
       <c r="N75">
-        <v>-6.904409680327538</v>
+        <v>-9.539092438054036</v>
       </c>
       <c r="O75">
-        <v>-1.726102420081884</v>
+        <v>-2.384773109513509</v>
       </c>
       <c r="P75">
-        <v>-5.178307260245653</v>
+        <v>-7.154319328540527</v>
       </c>
       <c r="Q75">
-        <v>-0.8483072602456527</v>
+        <v>-2.824319328540527</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2104117079042525</v>
+        <v>0.2192967148200383</v>
       </c>
       <c r="T75">
-        <v>3.208588578664681</v>
+        <v>3.381773901108021</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1252672843227293</v>
+        <v>0.105232214686994</v>
       </c>
       <c r="W75">
-        <v>0.175646329307996</v>
+        <v>0.2109862437768068</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5010691372909174</v>
+        <v>0.420928858747976</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.213146966248047</v>
+        <v>0.215046966248047</v>
       </c>
       <c r="C76">
-        <v>-22.86014663377033</v>
+        <v>-24.12961928216817</v>
       </c>
       <c r="D76">
-        <v>36.60029627570395</v>
+        <v>36.27488366662331</v>
       </c>
       <c r="E76">
-        <v>62.8544389777523</v>
+        <v>63.7984990170695</v>
       </c>
       <c r="F76">
-        <v>69.86044290947427</v>
+        <v>70.80450294879148</v>
       </c>
       <c r="G76">
         <v>10.4</v>
@@ -7519,37 +7519,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M76">
-        <v>16.47309243805404</v>
+        <v>16.69570179532503</v>
       </c>
       <c r="N76">
-        <v>-9.539092438054036</v>
+        <v>-9.761701795325033</v>
       </c>
       <c r="O76">
-        <v>-2.384773109513509</v>
+        <v>-2.440425448831258</v>
       </c>
       <c r="P76">
-        <v>-7.154319328540527</v>
+        <v>-7.321276346493775</v>
       </c>
       <c r="Q76">
-        <v>-2.824319328540527</v>
+        <v>-2.991276346493775</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2192967148200383</v>
+        <v>0.2262365834128398</v>
       </c>
       <c r="T76">
-        <v>3.381773901108021</v>
+        <v>3.517044857152342</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.105232214686994</v>
+        <v>0.1038291184911675</v>
       </c>
       <c r="W76">
-        <v>0.2109862437768068</v>
+        <v>0.2113170938597827</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.420928858747976</v>
+        <v>0.4153164739646698</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.215046966248047</v>
+        <v>0.216946966248047</v>
       </c>
       <c r="C77">
-        <v>-24.12961928216817</v>
+        <v>-25.39335644873798</v>
       </c>
       <c r="D77">
-        <v>36.27488366662331</v>
+        <v>35.95520653937073</v>
       </c>
       <c r="E77">
-        <v>63.7984990170695</v>
+        <v>64.74255905638672</v>
       </c>
       <c r="F77">
-        <v>70.80450294879148</v>
+        <v>71.7485629881087</v>
       </c>
       <c r="G77">
         <v>10.4</v>
@@ -7601,37 +7601,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M77">
-        <v>16.69570179532503</v>
+        <v>16.91831115259603</v>
       </c>
       <c r="N77">
-        <v>-9.761701795325033</v>
+        <v>-9.984311152596034</v>
       </c>
       <c r="O77">
-        <v>-2.440425448831258</v>
+        <v>-2.496077788149008</v>
       </c>
       <c r="P77">
-        <v>-7.321276346493775</v>
+        <v>-7.488233364447025</v>
       </c>
       <c r="Q77">
-        <v>-2.991276346493775</v>
+        <v>-3.158233364447025</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2262365834128398</v>
+        <v>0.2337547743883748</v>
       </c>
       <c r="T77">
-        <v>3.517044857152342</v>
+        <v>3.663588392867023</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1038291184911675</v>
+        <v>0.1024629458794416</v>
       </c>
       <c r="W77">
-        <v>0.2113170938597827</v>
+        <v>0.2116392373616277</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4153164739646698</v>
+        <v>0.4098517835177662</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.216946966248047</v>
+        <v>0.218846966248047</v>
       </c>
       <c r="C78">
-        <v>-25.39335644873798</v>
+        <v>-26.65150844289573</v>
       </c>
       <c r="D78">
-        <v>35.95520653937073</v>
+        <v>35.64111458453019</v>
       </c>
       <c r="E78">
-        <v>64.74255905638672</v>
+        <v>65.68661909570395</v>
       </c>
       <c r="F78">
-        <v>71.7485629881087</v>
+        <v>72.69262302742592</v>
       </c>
       <c r="G78">
         <v>10.4</v>
@@ -7683,37 +7683,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M78">
-        <v>16.91831115259603</v>
+        <v>17.14092050986703</v>
       </c>
       <c r="N78">
-        <v>-9.984311152596034</v>
+        <v>-10.20692050986703</v>
       </c>
       <c r="O78">
-        <v>-2.496077788149008</v>
+        <v>-2.551730127466759</v>
       </c>
       <c r="P78">
-        <v>-7.488233364447025</v>
+        <v>-7.655190382400276</v>
       </c>
       <c r="Q78">
-        <v>-3.158233364447025</v>
+        <v>-3.325190382400276</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2337547743883748</v>
+        <v>0.2419267211009128</v>
       </c>
       <c r="T78">
-        <v>3.663588392867023</v>
+        <v>3.822874844730807</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1024629458794416</v>
+        <v>0.1011322582706176</v>
       </c>
       <c r="W78">
-        <v>0.2116392373616277</v>
+        <v>0.2119530134997884</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4098517835177662</v>
+        <v>0.4045290330824706</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.218846966248047</v>
+        <v>0.220746966248047</v>
       </c>
       <c r="C79">
-        <v>-26.65150844289573</v>
+        <v>-27.90422036734211</v>
       </c>
       <c r="D79">
-        <v>35.64111458453019</v>
+        <v>35.33246269940103</v>
       </c>
       <c r="E79">
-        <v>65.68661909570395</v>
+        <v>66.63067913502117</v>
       </c>
       <c r="F79">
-        <v>72.69262302742592</v>
+        <v>73.63668306674315</v>
       </c>
       <c r="G79">
         <v>10.4</v>
@@ -7765,37 +7765,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M79">
-        <v>17.14092050986703</v>
+        <v>17.36352986713803</v>
       </c>
       <c r="N79">
-        <v>-10.20692050986703</v>
+        <v>-10.42952986713803</v>
       </c>
       <c r="O79">
-        <v>-2.551730127466759</v>
+        <v>-2.607382466784509</v>
       </c>
       <c r="P79">
-        <v>-7.655190382400276</v>
+        <v>-7.822147400353526</v>
       </c>
       <c r="Q79">
-        <v>-3.325190382400276</v>
+        <v>-3.492147400353526</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2419267211009128</v>
+        <v>0.2508415720600452</v>
       </c>
       <c r="T79">
-        <v>3.822874844730807</v>
+        <v>3.996641883127662</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1011322582706176</v>
+        <v>0.09983569085689177</v>
       </c>
       <c r="W79">
-        <v>0.2119530134997884</v>
+        <v>0.2122587440959449</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4045290330824706</v>
+        <v>0.3993427634275671</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.220746966248047</v>
+        <v>0.222646966248047</v>
       </c>
       <c r="C80">
-        <v>-27.90422036734211</v>
+        <v>-29.15163234157745</v>
       </c>
       <c r="D80">
-        <v>35.33246269940103</v>
+        <v>35.02911076448292</v>
       </c>
       <c r="E80">
-        <v>66.63067913502117</v>
+        <v>67.57473917433839</v>
       </c>
       <c r="F80">
-        <v>73.63668306674315</v>
+        <v>74.58074310606037</v>
       </c>
       <c r="G80">
         <v>10.4</v>
@@ -7847,37 +7847,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M80">
-        <v>17.36352986713803</v>
+        <v>17.58613922440903</v>
       </c>
       <c r="N80">
-        <v>-10.42952986713803</v>
+        <v>-10.65213922440904</v>
       </c>
       <c r="O80">
-        <v>-2.607382466784509</v>
+        <v>-2.663034806102259</v>
       </c>
       <c r="P80">
-        <v>-7.822147400353526</v>
+        <v>-7.989104418306777</v>
       </c>
       <c r="Q80">
-        <v>-3.492147400353526</v>
+        <v>-3.659104418306777</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2508415720600452</v>
+        <v>0.260605456443857</v>
       </c>
       <c r="T80">
-        <v>3.996641883127662</v>
+        <v>4.186958163276599</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09983569085689177</v>
+        <v>0.09857194793465264</v>
       </c>
       <c r="W80">
-        <v>0.2122587440959449</v>
+        <v>0.2125567346770089</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3993427634275671</v>
+        <v>0.3942877917386105</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.222646966248047</v>
+        <v>0.224546966248047</v>
       </c>
       <c r="C81">
-        <v>-29.15163234157745</v>
+        <v>-30.39387971400067</v>
       </c>
       <c r="D81">
-        <v>35.02911076448292</v>
+        <v>34.73092343137692</v>
       </c>
       <c r="E81">
-        <v>67.57473917433839</v>
+        <v>68.51879921365561</v>
       </c>
       <c r="F81">
-        <v>74.58074310606037</v>
+        <v>75.52480314537759</v>
       </c>
       <c r="G81">
         <v>10.4</v>
@@ -7929,37 +7929,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M81">
-        <v>17.58613922440903</v>
+        <v>17.80874858168004</v>
       </c>
       <c r="N81">
-        <v>-10.65213922440904</v>
+        <v>-10.87474858168004</v>
       </c>
       <c r="O81">
-        <v>-2.663034806102259</v>
+        <v>-2.718687145420009</v>
       </c>
       <c r="P81">
-        <v>-7.989104418306777</v>
+        <v>-8.156061436260027</v>
       </c>
       <c r="Q81">
-        <v>-3.659104418306777</v>
+        <v>-3.826061436260026</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.260605456443857</v>
+        <v>0.2713457292660498</v>
       </c>
       <c r="T81">
-        <v>4.186958163276599</v>
+        <v>4.39630607144043</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09857194793465264</v>
+        <v>0.09733979858546947</v>
       </c>
       <c r="W81">
-        <v>0.2125567346770089</v>
+        <v>0.2128472754935463</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3942877917386105</v>
+        <v>0.3893591943418779</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.224546966248047</v>
+        <v>0.226446966248047</v>
       </c>
       <c r="C82">
-        <v>-30.39387971400067</v>
+        <v>-31.63109326326654</v>
       </c>
       <c r="D82">
-        <v>34.73092343137692</v>
+        <v>34.43776992142827</v>
       </c>
       <c r="E82">
-        <v>68.51879921365561</v>
+        <v>69.46285925297283</v>
       </c>
       <c r="F82">
-        <v>75.52480314537759</v>
+        <v>76.46886318469481</v>
       </c>
       <c r="G82">
         <v>10.4</v>
@@ -8011,37 +8011,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M82">
-        <v>17.80874858168004</v>
+        <v>18.03135793895104</v>
       </c>
       <c r="N82">
-        <v>-10.87474858168004</v>
+        <v>-11.09735793895104</v>
       </c>
       <c r="O82">
-        <v>-2.718687145420009</v>
+        <v>-2.774339484737759</v>
       </c>
       <c r="P82">
-        <v>-8.156061436260027</v>
+        <v>-8.323018454213278</v>
       </c>
       <c r="Q82">
-        <v>-3.826061436260026</v>
+        <v>-3.993018454213278</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2713457292660498</v>
+        <v>0.2832165571221577</v>
       </c>
       <c r="T82">
-        <v>4.39630607144043</v>
+        <v>4.627690601516241</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09733979858546947</v>
+        <v>0.09613807267700689</v>
       </c>
       <c r="W82">
-        <v>0.2128472754935463</v>
+        <v>0.2131306424627618</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3893591943418779</v>
+        <v>0.3845522907080275</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.226446966248047</v>
+        <v>0.228346966248047</v>
       </c>
       <c r="C83">
-        <v>-31.63109326326654</v>
+        <v>-32.86339938953085</v>
       </c>
       <c r="D83">
-        <v>34.43776992142827</v>
+        <v>34.14952383448119</v>
       </c>
       <c r="E83">
-        <v>69.46285925297283</v>
+        <v>70.40691929229006</v>
       </c>
       <c r="F83">
-        <v>76.46886318469481</v>
+        <v>77.41292322401203</v>
       </c>
       <c r="G83">
         <v>10.4</v>
@@ -8093,37 +8093,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M83">
-        <v>18.03135793895104</v>
+        <v>18.25396729622204</v>
       </c>
       <c r="N83">
-        <v>-11.09735793895104</v>
+        <v>-11.31996729622204</v>
       </c>
       <c r="O83">
-        <v>-2.774339484737759</v>
+        <v>-2.829991824055509</v>
       </c>
       <c r="P83">
-        <v>-8.323018454213278</v>
+        <v>-8.489975472166527</v>
       </c>
       <c r="Q83">
-        <v>-3.993018454213278</v>
+        <v>-4.159975472166527</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2832165571221577</v>
+        <v>0.2964063658511665</v>
       </c>
       <c r="T83">
-        <v>4.627690601516241</v>
+        <v>4.884784523822699</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09613807267700689</v>
+        <v>0.09496565715655558</v>
       </c>
       <c r="W83">
-        <v>0.2131306424627618</v>
+        <v>0.2134070980424842</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3845522907080275</v>
+        <v>0.3798626286262223</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.228346966248047</v>
+        <v>0.230246966248047</v>
       </c>
       <c r="C84">
-        <v>-32.86339938953085</v>
+        <v>-34.09092029617077</v>
       </c>
       <c r="D84">
-        <v>34.14952383448119</v>
+        <v>33.86606296715848</v>
       </c>
       <c r="E84">
-        <v>70.40691929229006</v>
+        <v>71.35097933160728</v>
       </c>
       <c r="F84">
-        <v>77.41292322401203</v>
+        <v>78.35698326332925</v>
       </c>
       <c r="G84">
         <v>10.4</v>
@@ -8175,37 +8175,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M84">
-        <v>18.25396729622204</v>
+        <v>18.47657665349304</v>
       </c>
       <c r="N84">
-        <v>-11.31996729622204</v>
+        <v>-11.54257665349304</v>
       </c>
       <c r="O84">
-        <v>-2.829991824055509</v>
+        <v>-2.88564416337326</v>
       </c>
       <c r="P84">
-        <v>-8.489975472166527</v>
+        <v>-8.656932490119781</v>
       </c>
       <c r="Q84">
-        <v>-4.159975472166527</v>
+        <v>-4.326932490119781</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2964063658511665</v>
+        <v>0.3111479167835881</v>
       </c>
       <c r="T84">
-        <v>4.884784523822699</v>
+        <v>5.172124789929917</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09496565715655558</v>
+        <v>0.09382149261250068</v>
       </c>
       <c r="W84">
-        <v>0.2134070980424842</v>
+        <v>0.2136768920419723</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3798626286262223</v>
+        <v>0.3752859704500027</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.230246966248047</v>
+        <v>0.232146966248047</v>
       </c>
       <c r="C85">
-        <v>-34.09092029617077</v>
+        <v>-35.31377416252943</v>
       </c>
       <c r="D85">
-        <v>33.86606296715848</v>
+        <v>33.58726914011704</v>
       </c>
       <c r="E85">
-        <v>71.35097933160728</v>
+        <v>72.2950393709245</v>
       </c>
       <c r="F85">
-        <v>78.35698326332925</v>
+        <v>79.30104330264648</v>
       </c>
       <c r="G85">
         <v>10.4</v>
@@ -8257,37 +8257,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M85">
-        <v>18.47657665349304</v>
+        <v>18.69918601076404</v>
       </c>
       <c r="N85">
-        <v>-11.54257665349304</v>
+        <v>-11.76518601076404</v>
       </c>
       <c r="O85">
-        <v>-2.88564416337326</v>
+        <v>-2.941296502691011</v>
       </c>
       <c r="P85">
-        <v>-8.656932490119781</v>
+        <v>-8.823889508073032</v>
       </c>
       <c r="Q85">
-        <v>-4.326932490119781</v>
+        <v>-4.493889508073032</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3111479167835881</v>
+        <v>0.3277321615825623</v>
       </c>
       <c r="T85">
-        <v>5.172124789929917</v>
+        <v>5.495382589300537</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09382149261250068</v>
+        <v>0.09270457008139948</v>
       </c>
       <c r="W85">
-        <v>0.2136768920419723</v>
+        <v>0.213940262374806</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3752859704500027</v>
+        <v>0.3708182803255979</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.232146966248047</v>
+        <v>0.234046966248047</v>
       </c>
       <c r="C86">
-        <v>-35.31377416252942</v>
+        <v>-36.53207530819783</v>
       </c>
       <c r="D86">
-        <v>33.58726914011704</v>
+        <v>33.31302803376586</v>
       </c>
       <c r="E86">
-        <v>72.29503937092448</v>
+        <v>73.23909941024171</v>
       </c>
       <c r="F86">
-        <v>79.30104330264646</v>
+        <v>80.24510334196368</v>
       </c>
       <c r="G86">
         <v>10.4</v>
@@ -8339,37 +8339,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M86">
-        <v>18.69918601076404</v>
+        <v>18.92179536803504</v>
       </c>
       <c r="N86">
-        <v>-11.76518601076404</v>
+        <v>-11.98779536803504</v>
       </c>
       <c r="O86">
-        <v>-2.94129650269101</v>
+        <v>-2.99694884200876</v>
       </c>
       <c r="P86">
-        <v>-8.823889508073028</v>
+        <v>-8.99084652602628</v>
       </c>
       <c r="Q86">
-        <v>-4.493889508073028</v>
+        <v>-4.66084652602628</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3277321615825622</v>
+        <v>0.3465276390213997</v>
       </c>
       <c r="T86">
-        <v>5.495382589300535</v>
+        <v>5.861741428587237</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0927045700813995</v>
+        <v>0.09161392808044186</v>
       </c>
       <c r="W86">
-        <v>0.213940262374806</v>
+        <v>0.2141974357586318</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3708182803255979</v>
+        <v>0.3664557123217674</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.234046966248047</v>
+        <v>0.235946966248047</v>
       </c>
       <c r="C87">
-        <v>-36.53207530819783</v>
+        <v>-37.7459343493136</v>
       </c>
       <c r="D87">
-        <v>33.31302803376586</v>
+        <v>33.04322903196731</v>
       </c>
       <c r="E87">
-        <v>73.23909941024171</v>
+        <v>74.18315944955893</v>
       </c>
       <c r="F87">
-        <v>80.24510334196368</v>
+        <v>81.18916338128091</v>
       </c>
       <c r="G87">
         <v>10.4</v>
@@ -8421,37 +8421,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M87">
-        <v>18.92179536803504</v>
+        <v>19.14440472530604</v>
       </c>
       <c r="N87">
-        <v>-11.98779536803504</v>
+        <v>-12.21040472530604</v>
       </c>
       <c r="O87">
-        <v>-2.99694884200876</v>
+        <v>-3.05260118132651</v>
       </c>
       <c r="P87">
-        <v>-8.99084652602628</v>
+        <v>-9.157803543979529</v>
       </c>
       <c r="Q87">
-        <v>-4.66084652602628</v>
+        <v>-4.827803543979529</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3465276390213997</v>
+        <v>0.3680081846657854</v>
       </c>
       <c r="T87">
-        <v>5.861741428587237</v>
+        <v>6.280437244914897</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09161392808044186</v>
+        <v>0.09054864984694834</v>
       </c>
       <c r="W87">
-        <v>0.2141974357586318</v>
+        <v>0.2144486283660896</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3664557123217674</v>
+        <v>0.3621945993877934</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.235946966248047</v>
+        <v>0.237846966248047</v>
       </c>
       <c r="C88">
-        <v>-37.7459343493136</v>
+        <v>-38.95545834732566</v>
       </c>
       <c r="D88">
-        <v>33.04322903196731</v>
+        <v>32.77776507327247</v>
       </c>
       <c r="E88">
-        <v>74.18315944955893</v>
+        <v>75.12721948887615</v>
       </c>
       <c r="F88">
-        <v>81.18916338128091</v>
+        <v>82.13322342059813</v>
       </c>
       <c r="G88">
         <v>10.4</v>
@@ -8503,37 +8503,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M88">
-        <v>19.14440472530604</v>
+        <v>19.36701408257704</v>
       </c>
       <c r="N88">
-        <v>-12.21040472530604</v>
+        <v>-12.43301408257704</v>
       </c>
       <c r="O88">
-        <v>-3.05260118132651</v>
+        <v>-3.10825352064426</v>
       </c>
       <c r="P88">
-        <v>-9.157803543979529</v>
+        <v>-9.324760561932781</v>
       </c>
       <c r="Q88">
-        <v>-4.827803543979529</v>
+        <v>-4.994760561932781</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3680081846657854</v>
+        <v>0.3927934296400765</v>
       </c>
       <c r="T88">
-        <v>6.280437244914897</v>
+        <v>6.763547802216042</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09054864984694834</v>
+        <v>0.08950786076824779</v>
       </c>
       <c r="W88">
-        <v>0.2144486283660896</v>
+        <v>0.2146940464308472</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3621945993877934</v>
+        <v>0.3580314430729912</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.237846966248047</v>
+        <v>0.239746966248047</v>
       </c>
       <c r="C89">
-        <v>-38.95545834732566</v>
+        <v>-40.16075095064532</v>
       </c>
       <c r="D89">
-        <v>32.77776507327247</v>
+        <v>32.51653250927003</v>
       </c>
       <c r="E89">
-        <v>75.12721948887615</v>
+        <v>76.07127952819337</v>
       </c>
       <c r="F89">
-        <v>82.13322342059813</v>
+        <v>83.07728345991535</v>
       </c>
       <c r="G89">
         <v>10.4</v>
@@ -8585,37 +8585,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M89">
-        <v>19.36701408257704</v>
+        <v>19.58962343984804</v>
       </c>
       <c r="N89">
-        <v>-12.43301408257704</v>
+        <v>-12.65562343984804</v>
       </c>
       <c r="O89">
-        <v>-3.10825352064426</v>
+        <v>-3.16390585996201</v>
       </c>
       <c r="P89">
-        <v>-9.324760561932781</v>
+        <v>-9.49171757988603</v>
       </c>
       <c r="Q89">
-        <v>-4.994760561932781</v>
+        <v>-5.16171757988603</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3927934296400765</v>
+        <v>0.4217095487767497</v>
       </c>
       <c r="T89">
-        <v>6.763547802216042</v>
+        <v>7.327176785734047</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08950786076824779</v>
+        <v>0.08849072598679042</v>
       </c>
       <c r="W89">
-        <v>0.2146940464308472</v>
+        <v>0.2149338868123148</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3580314430729912</v>
+        <v>0.3539629039471617</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.239746966248047</v>
+        <v>0.241646966248047</v>
       </c>
       <c r="C90">
-        <v>-40.16075095064532</v>
+        <v>-41.3619125295771</v>
       </c>
       <c r="D90">
-        <v>32.51653250927003</v>
+        <v>32.25943096965547</v>
       </c>
       <c r="E90">
-        <v>76.07127952819337</v>
+        <v>77.01533956751059</v>
       </c>
       <c r="F90">
-        <v>83.07728345991535</v>
+        <v>84.02134349923257</v>
       </c>
       <c r="G90">
         <v>10.4</v>
@@ -8667,37 +8667,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M90">
-        <v>19.58962343984804</v>
+        <v>19.81223279711904</v>
       </c>
       <c r="N90">
-        <v>-12.65562343984804</v>
+        <v>-12.87823279711904</v>
       </c>
       <c r="O90">
-        <v>-3.16390585996201</v>
+        <v>-3.21955819927976</v>
       </c>
       <c r="P90">
-        <v>-9.49171757988603</v>
+        <v>-9.658674597839282</v>
       </c>
       <c r="Q90">
-        <v>-5.16171757988603</v>
+        <v>-5.328674597839282</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4217095487767497</v>
+        <v>0.4558831441200905</v>
       </c>
       <c r="T90">
-        <v>7.327176785734047</v>
+        <v>7.993283766255325</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08849072598679042</v>
+        <v>0.08749644816671413</v>
       </c>
       <c r="W90">
-        <v>0.2149338868123148</v>
+        <v>0.2151683375222888</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3539629039471617</v>
+        <v>0.3499857926668565</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.241646966248047</v>
+        <v>0.243546966248047</v>
       </c>
       <c r="C91">
-        <v>-41.3619125295771</v>
+        <v>-42.55904030489872</v>
       </c>
       <c r="D91">
-        <v>32.25943096965547</v>
+        <v>32.00636323365107</v>
       </c>
       <c r="E91">
-        <v>77.01533956751059</v>
+        <v>77.95939960682782</v>
       </c>
       <c r="F91">
-        <v>84.02134349923257</v>
+        <v>84.96540353854979</v>
       </c>
       <c r="G91">
         <v>10.4</v>
@@ -8749,37 +8749,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M91">
-        <v>19.81223279711904</v>
+        <v>20.03484215439004</v>
       </c>
       <c r="N91">
-        <v>-12.87823279711904</v>
+        <v>-13.10084215439004</v>
       </c>
       <c r="O91">
-        <v>-3.21955819927976</v>
+        <v>-3.275210538597511</v>
       </c>
       <c r="P91">
-        <v>-9.658674597839282</v>
+        <v>-9.825631615792531</v>
       </c>
       <c r="Q91">
-        <v>-5.328674597839282</v>
+        <v>-5.495631615792531</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4558831441200905</v>
+        <v>0.4968914585320997</v>
       </c>
       <c r="T91">
-        <v>7.993283766255325</v>
+        <v>8.792612142880859</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08749644816671413</v>
+        <v>0.08652426540930619</v>
       </c>
       <c r="W91">
-        <v>0.2151683375222888</v>
+        <v>0.2153975782164856</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3499857926668565</v>
+        <v>0.3460970616372248</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.243546966248047</v>
+        <v>0.245446966248047</v>
       </c>
       <c r="C92">
-        <v>-42.55904030489872</v>
+        <v>-43.75222847043604</v>
       </c>
       <c r="D92">
-        <v>32.00636323365107</v>
+        <v>31.75723510743096</v>
       </c>
       <c r="E92">
-        <v>77.95939960682782</v>
+        <v>78.90345964614502</v>
       </c>
       <c r="F92">
-        <v>84.96540353854979</v>
+        <v>85.909463577867</v>
       </c>
       <c r="G92">
         <v>10.4</v>
@@ -8831,37 +8831,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M92">
-        <v>20.03484215439004</v>
+        <v>20.25745151166104</v>
       </c>
       <c r="N92">
-        <v>-13.10084215439004</v>
+        <v>-13.32345151166104</v>
       </c>
       <c r="O92">
-        <v>-3.275210538597511</v>
+        <v>-3.33086287791526</v>
       </c>
       <c r="P92">
-        <v>-9.825631615792531</v>
+        <v>-9.992588633745779</v>
       </c>
       <c r="Q92">
-        <v>-5.495631615792531</v>
+        <v>-5.662588633745779</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4968914585320997</v>
+        <v>0.5470127317023329</v>
       </c>
       <c r="T92">
-        <v>8.792612142880859</v>
+        <v>9.769569047645398</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08652426540930619</v>
+        <v>0.08557344930590724</v>
       </c>
       <c r="W92">
-        <v>0.2153975782164856</v>
+        <v>0.2156217806536671</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3460970616372248</v>
+        <v>0.342293797223629</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.245446966248047</v>
+        <v>0.247346966248047</v>
       </c>
       <c r="C93">
-        <v>-43.75222847043604</v>
+        <v>-44.94156830995771</v>
       </c>
       <c r="D93">
-        <v>31.75723510743096</v>
+        <v>31.51195530722651</v>
       </c>
       <c r="E93">
-        <v>78.90345964614502</v>
+        <v>79.84751968546225</v>
       </c>
       <c r="F93">
-        <v>85.909463577867</v>
+        <v>86.85352361718422</v>
       </c>
       <c r="G93">
         <v>10.4</v>
@@ -8913,37 +8913,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M93">
-        <v>20.25745151166104</v>
+        <v>20.48006086893204</v>
       </c>
       <c r="N93">
-        <v>-13.32345151166104</v>
+        <v>-13.54606086893204</v>
       </c>
       <c r="O93">
-        <v>-3.33086287791526</v>
+        <v>-3.38651521723301</v>
       </c>
       <c r="P93">
-        <v>-9.992588633745779</v>
+        <v>-10.15954565169903</v>
       </c>
       <c r="Q93">
-        <v>-5.662588633745779</v>
+        <v>-5.82954565169903</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5470127317023329</v>
+        <v>0.6096643231651245</v>
       </c>
       <c r="T93">
-        <v>9.769569047645398</v>
+        <v>10.99076517860107</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08557344930590724</v>
+        <v>0.08464330311779955</v>
       </c>
       <c r="W93">
-        <v>0.2156217806536671</v>
+        <v>0.2158411091248229</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.342293797223629</v>
+        <v>0.3385732124711982</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.247346966248047</v>
+        <v>0.249246966248047</v>
       </c>
       <c r="C94">
-        <v>-44.94156830995771</v>
+        <v>-46.12714830869425</v>
       </c>
       <c r="D94">
-        <v>31.51195530722651</v>
+        <v>31.2704353478072</v>
       </c>
       <c r="E94">
-        <v>79.84751968546225</v>
+        <v>80.79157972477947</v>
       </c>
       <c r="F94">
-        <v>86.85352361718422</v>
+        <v>87.79758365650144</v>
       </c>
       <c r="G94">
         <v>10.4</v>
@@ -8995,37 +8995,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M94">
-        <v>20.48006086893204</v>
+        <v>20.70267022620304</v>
       </c>
       <c r="N94">
-        <v>-13.54606086893204</v>
+        <v>-13.76867022620304</v>
       </c>
       <c r="O94">
-        <v>-3.38651521723301</v>
+        <v>-3.44216755655076</v>
       </c>
       <c r="P94">
-        <v>-10.15954565169903</v>
+        <v>-10.32650266965228</v>
       </c>
       <c r="Q94">
-        <v>-5.82954565169903</v>
+        <v>-5.99650266965228</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6096643231651245</v>
+        <v>0.690216369331571</v>
       </c>
       <c r="T94">
-        <v>10.99076517860107</v>
+        <v>12.5608744898298</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08464330311779955</v>
+        <v>0.08373316007352213</v>
       </c>
       <c r="W94">
-        <v>0.2158411091248229</v>
+        <v>0.2160557208546635</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3385732124711982</v>
+        <v>0.3349326402940885</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.249246966248047</v>
+        <v>0.251146966248047</v>
       </c>
       <c r="C95">
-        <v>-46.12714830869425</v>
+        <v>-47.30905425976778</v>
       </c>
       <c r="D95">
-        <v>31.2704353478072</v>
+        <v>31.03258943605089</v>
       </c>
       <c r="E95">
-        <v>80.79157972477947</v>
+        <v>81.73563976409669</v>
       </c>
       <c r="F95">
-        <v>87.79758365650144</v>
+        <v>88.74164369581867</v>
       </c>
       <c r="G95">
         <v>10.4</v>
@@ -9077,37 +9077,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M95">
-        <v>20.70267022620304</v>
+        <v>20.92527958347404</v>
       </c>
       <c r="N95">
-        <v>-13.76867022620304</v>
+        <v>-13.99127958347404</v>
       </c>
       <c r="O95">
-        <v>-3.44216755655076</v>
+        <v>-3.497819895868511</v>
       </c>
       <c r="P95">
-        <v>-10.32650266965228</v>
+        <v>-10.49345968760553</v>
       </c>
       <c r="Q95">
-        <v>-5.99650266965228</v>
+        <v>-6.163459687605533</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.690216369331571</v>
+        <v>0.7976190975534998</v>
       </c>
       <c r="T95">
-        <v>12.5608744898298</v>
+        <v>14.65435357146811</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08373316007352213</v>
+        <v>0.08284238177486763</v>
       </c>
       <c r="W95">
-        <v>0.2160557208546635</v>
+        <v>0.2162657663774862</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3349326402940885</v>
+        <v>0.3313695270994705</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.251146966248047</v>
+        <v>0.253046966248047</v>
       </c>
       <c r="C96">
-        <v>-47.30905425976778</v>
+        <v>-48.48736936580136</v>
       </c>
       <c r="D96">
-        <v>31.03258943605089</v>
+        <v>30.79833436933453</v>
       </c>
       <c r="E96">
-        <v>81.73563976409669</v>
+        <v>82.67969980341391</v>
       </c>
       <c r="F96">
-        <v>88.74164369581867</v>
+        <v>89.68570373513589</v>
       </c>
       <c r="G96">
         <v>10.4</v>
@@ -9159,37 +9159,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M96">
-        <v>20.92527958347404</v>
+        <v>21.14788894074504</v>
       </c>
       <c r="N96">
-        <v>-13.99127958347404</v>
+        <v>-14.21388894074505</v>
       </c>
       <c r="O96">
-        <v>-3.497819895868511</v>
+        <v>-3.553472235186261</v>
       </c>
       <c r="P96">
-        <v>-10.49345968760553</v>
+        <v>-10.66041670555878</v>
       </c>
       <c r="Q96">
-        <v>-6.163459687605533</v>
+        <v>-6.330416705558784</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7976190975534998</v>
+        <v>0.9479829170642002</v>
       </c>
       <c r="T96">
-        <v>14.65435357146811</v>
+        <v>17.58522428576174</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08284238177486763</v>
+        <v>0.08197035670355324</v>
       </c>
       <c r="W96">
-        <v>0.2162657663774862</v>
+        <v>0.2164713898893021</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3313695270994705</v>
+        <v>0.327881426814213</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.253046966248047</v>
+        <v>0.254946966248047</v>
       </c>
       <c r="C97">
-        <v>-48.48736936580136</v>
+        <v>-49.66217433596066</v>
       </c>
       <c r="D97">
-        <v>30.79833436933453</v>
+        <v>30.56758943849245</v>
       </c>
       <c r="E97">
-        <v>82.67969980341391</v>
+        <v>83.62375984273113</v>
       </c>
       <c r="F97">
-        <v>89.68570373513589</v>
+        <v>90.62976377445311</v>
       </c>
       <c r="G97">
         <v>10.4</v>
@@ -9241,37 +9241,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M97">
-        <v>21.14788894074504</v>
+        <v>21.37049829801605</v>
       </c>
       <c r="N97">
-        <v>-14.21388894074505</v>
+        <v>-14.43649829801605</v>
       </c>
       <c r="O97">
-        <v>-3.553472235186261</v>
+        <v>-3.609124574504011</v>
       </c>
       <c r="P97">
-        <v>-10.66041670555878</v>
+        <v>-10.82737372351203</v>
       </c>
       <c r="Q97">
-        <v>-6.330416705558784</v>
+        <v>-6.497373723512034</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9479829170642002</v>
+        <v>1.173528646330251</v>
       </c>
       <c r="T97">
-        <v>17.58522428576174</v>
+        <v>21.98153035720218</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08197035670355324</v>
+        <v>0.08111649882122456</v>
       </c>
       <c r="W97">
-        <v>0.2164713898893021</v>
+        <v>0.2166727295779553</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.327881426814213</v>
+        <v>0.3244659952848982</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.254946966248047</v>
+        <v>0.256846966248047</v>
       </c>
       <c r="C98">
-        <v>-49.66217433596064</v>
+        <v>-50.83354747866581</v>
       </c>
       <c r="D98">
-        <v>30.56758943849245</v>
+        <v>30.34027633510451</v>
       </c>
       <c r="E98">
-        <v>83.62375984273112</v>
+        <v>84.56781988204834</v>
       </c>
       <c r="F98">
-        <v>90.6297637744531</v>
+        <v>91.57382381377032</v>
       </c>
       <c r="G98">
         <v>10.4</v>
@@ -9323,37 +9323,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M98">
-        <v>21.37049829801604</v>
+        <v>21.59310765528704</v>
       </c>
       <c r="N98">
-        <v>-14.43649829801604</v>
+        <v>-14.65910765528704</v>
       </c>
       <c r="O98">
-        <v>-3.609124574504011</v>
+        <v>-3.664776913821761</v>
       </c>
       <c r="P98">
-        <v>-10.82737372351203</v>
+        <v>-10.99433074146528</v>
       </c>
       <c r="Q98">
-        <v>-6.497373723512032</v>
+        <v>-6.664330741465282</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.173528646330248</v>
+        <v>1.549438195106997</v>
       </c>
       <c r="T98">
-        <v>21.98153035720212</v>
+        <v>29.30870714293616</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08111649882122457</v>
+        <v>0.0802802462560573</v>
       </c>
       <c r="W98">
-        <v>0.2166727295779553</v>
+        <v>0.2168699179328217</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3244659952848983</v>
+        <v>0.3211209850242293</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.256846966248047</v>
+        <v>0.258746966248047</v>
       </c>
       <c r="C99">
-        <v>-50.83354747866581</v>
+        <v>-52.0015647901972</v>
       </c>
       <c r="D99">
-        <v>30.34027633510451</v>
+        <v>30.11631906289034</v>
       </c>
       <c r="E99">
-        <v>84.56781988204834</v>
+        <v>85.51187992136556</v>
       </c>
       <c r="F99">
-        <v>91.57382381377032</v>
+        <v>92.51788385308754</v>
       </c>
       <c r="G99">
         <v>10.4</v>
@@ -9405,37 +9405,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M99">
-        <v>21.59310765528704</v>
+        <v>21.81571701255804</v>
       </c>
       <c r="N99">
-        <v>-14.65910765528704</v>
+        <v>-14.88171701255804</v>
       </c>
       <c r="O99">
-        <v>-3.664776913821761</v>
+        <v>-3.720429253139511</v>
       </c>
       <c r="P99">
-        <v>-10.99433074146528</v>
+        <v>-11.16128775941853</v>
       </c>
       <c r="Q99">
-        <v>-6.664330741465282</v>
+        <v>-6.831287759418533</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.549438195106997</v>
+        <v>2.301257292660496</v>
       </c>
       <c r="T99">
-        <v>29.30870714293616</v>
+        <v>43.96306071440425</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0802802462560573</v>
+        <v>0.07946106006977099</v>
       </c>
       <c r="W99">
-        <v>0.2168699179328217</v>
+        <v>0.217063082035548</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3211209850242293</v>
+        <v>0.317844240279084</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.258746966248047</v>
+        <v>0.260646966248047</v>
       </c>
       <c r="C100">
-        <v>-52.0015647901972</v>
+        <v>-53.16630003940554</v>
       </c>
       <c r="D100">
-        <v>30.11631906289034</v>
+        <v>29.89564385299922</v>
       </c>
       <c r="E100">
-        <v>85.51187992136556</v>
+        <v>86.45593996068278</v>
       </c>
       <c r="F100">
-        <v>92.51788385308754</v>
+        <v>93.46194389240476</v>
       </c>
       <c r="G100">
         <v>10.4</v>
@@ -9487,37 +9487,37 @@
         <v>6.933999999999999</v>
       </c>
       <c r="M100">
-        <v>21.81571701255804</v>
+        <v>22.03832636982904</v>
       </c>
       <c r="N100">
-        <v>-14.88171701255804</v>
+        <v>-15.10432636982904</v>
       </c>
       <c r="O100">
-        <v>-3.720429253139511</v>
+        <v>-3.776081592457261</v>
       </c>
       <c r="P100">
-        <v>-11.16128775941853</v>
+        <v>-11.32824477737178</v>
       </c>
       <c r="Q100">
-        <v>-6.831287759418533</v>
+        <v>-6.998244777371783</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.301257292660496</v>
+        <v>4.556714585320992</v>
       </c>
       <c r="T100">
-        <v>43.96306071440425</v>
+        <v>87.9261214288085</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07946106006977099</v>
+        <v>0.07865842309936927</v>
       </c>
       <c r="W100">
-        <v>0.217063082035548</v>
+        <v>0.2172523438331687</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.317844240279084</v>
+        <v>0.3146336923974771</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.260646966248047</v>
-      </c>
-      <c r="C101">
-        <v>-53.16630003940554</v>
-      </c>
-      <c r="D101">
-        <v>29.89564385299922</v>
-      </c>
-      <c r="E101">
-        <v>86.45593996068278</v>
-      </c>
-      <c r="F101">
-        <v>93.46194389240476</v>
-      </c>
-      <c r="G101">
-        <v>10.4</v>
-      </c>
-      <c r="H101">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.264</v>
-      </c>
-      <c r="K101">
-        <v>4.33</v>
-      </c>
-      <c r="L101">
-        <v>6.933999999999999</v>
-      </c>
-      <c r="M101">
-        <v>22.03832636982904</v>
-      </c>
-      <c r="N101">
-        <v>-15.10432636982904</v>
-      </c>
-      <c r="O101">
-        <v>-3.776081592457261</v>
-      </c>
-      <c r="P101">
-        <v>-11.32824477737178</v>
-      </c>
-      <c r="Q101">
-        <v>-6.998244777371783</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.556714585320992</v>
-      </c>
-      <c r="T101">
-        <v>87.9261214288085</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07865842309936927</v>
-      </c>
-      <c r="W101">
-        <v>0.2172523438331687</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3146336923974771</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
